--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131025505</v>
+        <v>131025514</v>
       </c>
       <c r="B2" t="n">
         <v>79244</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464214</v>
+        <v>464434</v>
       </c>
       <c r="R2" t="n">
-        <v>7042578</v>
+        <v>7042377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På flera granar vid en lucka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131025514</v>
+        <v>131024454</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464434</v>
+        <v>464321</v>
       </c>
       <c r="R3" t="n">
-        <v>7042377</v>
+        <v>7042482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar vid en lucka.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131024454</v>
+        <v>131025505</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464321</v>
+        <v>464214</v>
       </c>
       <c r="R4" t="n">
-        <v>7042482</v>
+        <v>7042578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131025513</v>
+        <v>131024469</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464484</v>
+        <v>464325</v>
       </c>
       <c r="R5" t="n">
-        <v>7042425</v>
+        <v>7042323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025526</v>
+        <v>131025467</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464101</v>
+        <v>464403</v>
       </c>
       <c r="R6" t="n">
-        <v>7042665</v>
+        <v>7042578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1166,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, färska och äldre, tydliga på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1169,6 +1177,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1185,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131025467</v>
+        <v>131025513</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,42 +1229,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464403</v>
+        <v>464484</v>
       </c>
       <c r="R7" t="n">
-        <v>7042578</v>
+        <v>7042425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,7 +1293,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, tydliga på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,31 +1304,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1320,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131024469</v>
+        <v>131025526</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,34 +1331,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464325</v>
+        <v>464101</v>
       </c>
       <c r="R8" t="n">
-        <v>7042323</v>
+        <v>7042665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,22 +1410,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025488</v>
+        <v>131025502</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,42 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463958</v>
+        <v>464177</v>
       </c>
       <c r="R9" t="n">
-        <v>7042484</v>
+        <v>7042606</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,31 +1508,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1659,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025502</v>
+        <v>131025519</v>
       </c>
       <c r="B11" t="n">
         <v>79244</v>
@@ -1694,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464177</v>
+        <v>464076</v>
       </c>
       <c r="R11" t="n">
-        <v>7042606</v>
+        <v>7042281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,7 +1728,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025519</v>
+        <v>131025512</v>
       </c>
       <c r="B12" t="n">
         <v>79244</v>
@@ -1796,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464076</v>
+        <v>464451</v>
       </c>
       <c r="R12" t="n">
-        <v>7042281</v>
+        <v>7042487</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1836,7 +1803,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,7 +1830,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025512</v>
+        <v>131025518</v>
       </c>
       <c r="B13" t="n">
         <v>79244</v>
@@ -1898,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464451</v>
+        <v>464161</v>
       </c>
       <c r="R13" t="n">
-        <v>7042487</v>
+        <v>7042247</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1965,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025518</v>
+        <v>131025494</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,23 +1943,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2000,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464161</v>
+        <v>464471</v>
       </c>
       <c r="R14" t="n">
-        <v>7042247</v>
+        <v>7042462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025463</v>
+        <v>131025488</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,16 +2041,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2100,7 +2063,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2110,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464211</v>
+        <v>463958</v>
       </c>
       <c r="R15" t="n">
-        <v>7042581</v>
+        <v>7042484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,7 +2113,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,7 +2127,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2202,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131025494</v>
+        <v>131024467</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,30 +2176,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464471</v>
+        <v>464322</v>
       </c>
       <c r="R16" t="n">
-        <v>7042462</v>
+        <v>7042355</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2240,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,19 +2255,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131024467</v>
+        <v>131025463</v>
       </c>
       <c r="B17" t="n">
         <v>57884</v>
@@ -2329,16 +2296,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464322</v>
+        <v>464211</v>
       </c>
       <c r="R17" t="n">
-        <v>7042355</v>
+        <v>7042581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,16 +2361,41 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131024476</v>
+        <v>131025528</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464255</v>
+        <v>464199</v>
       </c>
       <c r="R24" t="n">
-        <v>7042273</v>
+        <v>7042793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131025474</v>
+        <v>131024449</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3178,24 +3178,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464391</v>
+        <v>464183</v>
       </c>
       <c r="R25" t="n">
-        <v>7042299</v>
+        <v>7042531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3224,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,48 +3235,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131025470</v>
+        <v>131024476</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3313,24 +3280,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464484</v>
+        <v>464255</v>
       </c>
       <c r="R26" t="n">
-        <v>7042508</v>
+        <v>7042273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3326,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,48 +3337,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131024449</v>
+        <v>131025474</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3448,16 +3382,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464183</v>
+        <v>464391</v>
       </c>
       <c r="R27" t="n">
-        <v>7042531</v>
+        <v>7042299</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3494,7 +3436,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,23 +3447,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024474</v>
+        <v>131025470</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3550,16 +3517,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464280</v>
+        <v>464484</v>
       </c>
       <c r="R28" t="n">
-        <v>7042322</v>
+        <v>7042508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,7 +3571,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3607,23 +3582,48 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131025485</v>
+        <v>131024474</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3652,24 +3652,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464186</v>
+        <v>464280</v>
       </c>
       <c r="R29" t="n">
-        <v>7042779</v>
+        <v>7042322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3698,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3717,51 +3709,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025528</v>
+        <v>131025485</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,34 +3736,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464199</v>
+        <v>464186</v>
       </c>
       <c r="R30" t="n">
-        <v>7042793</v>
+        <v>7042779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3808,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3844,6 +3819,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025509</v>
+        <v>131024446</v>
       </c>
       <c r="B31" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,34 +3871,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464380</v>
+        <v>463828</v>
       </c>
       <c r="R31" t="n">
-        <v>7042615</v>
+        <v>7042514</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,14 +3943,14 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Gammalt bohål i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -3950,22 +3958,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131025522</v>
+        <v>131025464</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3973,34 +3981,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463978</v>
+        <v>464210</v>
       </c>
       <c r="R32" t="n">
-        <v>7042528</v>
+        <v>7042574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4037,7 +4053,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4048,6 +4064,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4064,10 +4105,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131024465</v>
+        <v>131025509</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4075,34 +4116,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464328</v>
+        <v>464380</v>
       </c>
       <c r="R33" t="n">
-        <v>7042367</v>
+        <v>7042615</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,7 +4180,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4154,22 +4195,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131024446</v>
+        <v>131025522</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4177,42 +4218,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463828</v>
+        <v>463978</v>
       </c>
       <c r="R34" t="n">
-        <v>7042514</v>
+        <v>7042528</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,14 +4282,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4264,19 +4297,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131025464</v>
+        <v>131024465</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4305,24 +4338,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464210</v>
+        <v>464328</v>
       </c>
       <c r="R35" t="n">
-        <v>7042574</v>
+        <v>7042367</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4384,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4370,41 +4395,16 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4648,7 +4648,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131024478</v>
+        <v>131025472</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4677,16 +4677,24 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464232</v>
+        <v>464419</v>
       </c>
       <c r="R38" t="n">
-        <v>7042762</v>
+        <v>7042316</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4723,7 +4731,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4734,26 +4742,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131025472</v>
+        <v>131025489</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,29 +4794,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4793,10 +4825,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464419</v>
+        <v>464035</v>
       </c>
       <c r="R39" t="n">
-        <v>7042316</v>
+        <v>7042354</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4865,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4842,6 +4874,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4852,22 +4885,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4885,10 +4918,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131025489</v>
+        <v>131025517</v>
       </c>
       <c r="B40" t="n">
-        <v>80350</v>
+        <v>79244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,41 +4929,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464035</v>
+        <v>464199</v>
       </c>
       <c r="R40" t="n">
-        <v>7042354</v>
+        <v>7042210</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4967,7 +4993,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4976,34 +5002,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5020,7 +5020,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131025517</v>
+        <v>131025527</v>
       </c>
       <c r="B41" t="n">
         <v>79244</v>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464199</v>
+        <v>464174</v>
       </c>
       <c r="R41" t="n">
-        <v>7042210</v>
+        <v>7042780</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025527</v>
+        <v>131024478</v>
       </c>
       <c r="B42" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,34 +5133,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464174</v>
+        <v>464232</v>
       </c>
       <c r="R42" t="n">
-        <v>7042780</v>
+        <v>7042762</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5212,12 +5212,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025524</v>
+        <v>131025478</v>
       </c>
       <c r="B47" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,34 +5676,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464041</v>
+        <v>464380</v>
       </c>
       <c r="R47" t="n">
-        <v>7042631</v>
+        <v>7042301</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5740,7 +5748,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,6 +5759,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5767,10 +5800,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025511</v>
+        <v>131025471</v>
       </c>
       <c r="B48" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5778,34 +5811,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464483</v>
+        <v>464444</v>
       </c>
       <c r="R48" t="n">
-        <v>7042518</v>
+        <v>7042363</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,7 +5883,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5853,6 +5894,36 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5869,10 +5940,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131024506</v>
+        <v>131025482</v>
       </c>
       <c r="B49" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5880,30 +5951,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464426</v>
+        <v>464034</v>
       </c>
       <c r="R49" t="n">
-        <v>7042565</v>
+        <v>7042322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5938,6 +6021,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5946,23 +6034,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025495</v>
+        <v>131024506</v>
       </c>
       <c r="B50" t="n">
         <v>91829</v>
@@ -5989,14 +6102,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>463986</v>
+        <v>464426</v>
       </c>
       <c r="R50" t="n">
-        <v>7042522</v>
+        <v>7042565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6031,11 +6144,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>I stående död klen gran.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6048,22 +6156,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025478</v>
+        <v>131025495</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6071,42 +6179,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464380</v>
+        <v>463986</v>
       </c>
       <c r="R51" t="n">
-        <v>7042301</v>
+        <v>7042522</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6143,7 +6239,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6154,31 +6250,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6195,10 +6266,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025471</v>
+        <v>131025524</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6206,42 +6277,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464444</v>
+        <v>464041</v>
       </c>
       <c r="R52" t="n">
-        <v>7042363</v>
+        <v>7042631</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,7 +6341,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6289,36 +6352,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6335,10 +6368,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025482</v>
+        <v>131025511</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6346,42 +6379,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464034</v>
+        <v>464483</v>
       </c>
       <c r="R53" t="n">
-        <v>7042322</v>
+        <v>7042518</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6443,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,31 +6454,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6470,10 +6470,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131024501</v>
+        <v>131025504</v>
       </c>
       <c r="B54" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,34 +6481,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464070</v>
+        <v>464204</v>
       </c>
       <c r="R54" t="n">
-        <v>7042517</v>
+        <v>7042559</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6543,6 +6543,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6555,22 +6560,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131024510</v>
+        <v>131024463</v>
       </c>
       <c r="B55" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6578,19 +6583,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6598,10 +6607,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464031</v>
+        <v>464371</v>
       </c>
       <c r="R55" t="n">
-        <v>7042403</v>
+        <v>7042397</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6634,6 +6643,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6660,10 +6674,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131025504</v>
+        <v>131025483</v>
       </c>
       <c r="B56" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6671,34 +6685,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464204</v>
+        <v>464021</v>
       </c>
       <c r="R56" t="n">
-        <v>7042559</v>
+        <v>7042325</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6735,7 +6757,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6746,6 +6768,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6762,10 +6809,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024511</v>
+        <v>131025469</v>
       </c>
       <c r="B57" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6773,30 +6820,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>463866</v>
+        <v>464464</v>
       </c>
       <c r="R57" t="n">
-        <v>7042468</v>
+        <v>7042544</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6831,6 +6890,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6839,23 +6903,48 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131024507</v>
+        <v>131024511</v>
       </c>
       <c r="B58" t="n">
         <v>91829</v>
@@ -6886,10 +6975,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464395</v>
+        <v>463866</v>
       </c>
       <c r="R58" t="n">
-        <v>7042406</v>
+        <v>7042468</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6948,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024463</v>
+        <v>131024510</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,23 +7048,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6983,10 +7068,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464371</v>
+        <v>464031</v>
       </c>
       <c r="R59" t="n">
-        <v>7042397</v>
+        <v>7042403</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7019,11 +7104,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7050,10 +7130,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131025483</v>
+        <v>131024507</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7061,42 +7141,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464021</v>
+        <v>464395</v>
       </c>
       <c r="R60" t="n">
-        <v>7042325</v>
+        <v>7042406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7131,11 +7199,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7144,51 +7207,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131025469</v>
+        <v>131024501</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>91805</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7196,42 +7234,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464464</v>
+        <v>464070</v>
       </c>
       <c r="R61" t="n">
-        <v>7042544</v>
+        <v>7042517</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7266,11 +7296,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7279,51 +7304,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131025508</v>
+        <v>131024460</v>
       </c>
       <c r="B62" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,34 +7331,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464310</v>
+        <v>464385</v>
       </c>
       <c r="R62" t="n">
-        <v>7042565</v>
+        <v>7042401</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7410,19 +7410,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131024460</v>
+        <v>131024450</v>
       </c>
       <c r="B63" t="n">
         <v>57884</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464385</v>
+        <v>464273</v>
       </c>
       <c r="R63" t="n">
-        <v>7042401</v>
+        <v>7042500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131024450</v>
+        <v>131025508</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7535,34 +7535,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464273</v>
+        <v>464310</v>
       </c>
       <c r="R64" t="n">
-        <v>7042500</v>
+        <v>7042565</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7614,22 +7614,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131024456</v>
+        <v>131024509</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7637,23 +7637,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7661,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464439</v>
+        <v>464214</v>
       </c>
       <c r="R65" t="n">
-        <v>7042505</v>
+        <v>7042282</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7697,11 +7693,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7728,10 +7719,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131024509</v>
+        <v>131024456</v>
       </c>
       <c r="B66" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,19 +7730,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7759,10 +7754,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464214</v>
+        <v>464439</v>
       </c>
       <c r="R66" t="n">
-        <v>7042282</v>
+        <v>7042505</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7795,6 +7790,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8506,10 +8506,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131025521</v>
+        <v>131024453</v>
       </c>
       <c r="B73" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8517,34 +8517,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464007</v>
+        <v>464327</v>
       </c>
       <c r="R73" t="n">
-        <v>7042409</v>
+        <v>7042477</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,19 +8596,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131024453</v>
+        <v>131024451</v>
       </c>
       <c r="B74" t="n">
         <v>57884</v>
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464327</v>
+        <v>464275</v>
       </c>
       <c r="R74" t="n">
-        <v>7042477</v>
+        <v>7042455</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131024451</v>
+        <v>131025480</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8739,16 +8739,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464275</v>
+        <v>464378</v>
       </c>
       <c r="R75" t="n">
-        <v>7042455</v>
+        <v>7042302</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8785,7 +8793,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8796,26 +8804,51 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131025480</v>
+        <v>131025521</v>
       </c>
       <c r="B76" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8823,42 +8856,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464378</v>
+        <v>464007</v>
       </c>
       <c r="R76" t="n">
-        <v>7042302</v>
+        <v>7042409</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8895,7 +8920,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8906,31 +8931,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8947,10 +8947,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131025490</v>
+        <v>131024470</v>
       </c>
       <c r="B77" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,41 +8958,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>463994</v>
+        <v>464325</v>
       </c>
       <c r="R77" t="n">
-        <v>7042378</v>
+        <v>7042334</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9029,7 +9022,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9038,51 +9031,25 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131024470</v>
+        <v>131024461</v>
       </c>
       <c r="B78" t="n">
         <v>57884</v>
@@ -9117,10 +9084,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464325</v>
+        <v>464377</v>
       </c>
       <c r="R78" t="n">
-        <v>7042334</v>
+        <v>7042402</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9157,7 +9124,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9184,10 +9151,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131024461</v>
+        <v>131025503</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9195,34 +9162,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464377</v>
+        <v>464158</v>
       </c>
       <c r="R79" t="n">
-        <v>7042402</v>
+        <v>7042548</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9259,7 +9226,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9274,12 +9241,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9421,10 +9388,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131025523</v>
+        <v>131025490</v>
       </c>
       <c r="B81" t="n">
-        <v>79244</v>
+        <v>80350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9432,34 +9399,41 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>463999</v>
+        <v>463994</v>
       </c>
       <c r="R81" t="n">
-        <v>7042559</v>
+        <v>7042378</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9496,7 +9470,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9505,8 +9479,34 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9523,7 +9523,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131025503</v>
+        <v>131025523</v>
       </c>
       <c r="B82" t="n">
         <v>79244</v>
@@ -9558,10 +9558,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464158</v>
+        <v>463999</v>
       </c>
       <c r="R82" t="n">
-        <v>7042548</v>
+        <v>7042559</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9718,10 +9718,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131025475</v>
+        <v>131024508</v>
       </c>
       <c r="B84" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9729,42 +9729,30 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464393</v>
+        <v>464083</v>
       </c>
       <c r="R84" t="n">
-        <v>7042284</v>
+        <v>7042298</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9799,11 +9787,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9812,51 +9795,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131024473</v>
+        <v>131025520</v>
       </c>
       <c r="B85" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9864,34 +9822,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464305</v>
+        <v>464027</v>
       </c>
       <c r="R85" t="n">
-        <v>7042334</v>
+        <v>7042318</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9928,7 +9886,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9943,19 +9901,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131025477</v>
+        <v>131025475</v>
       </c>
       <c r="B86" t="n">
         <v>57884</v>
@@ -9998,10 +9956,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464374</v>
+        <v>464393</v>
       </c>
       <c r="R86" t="n">
-        <v>7042300</v>
+        <v>7042284</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10038,7 +9996,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10090,10 +10048,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131024508</v>
+        <v>131024473</v>
       </c>
       <c r="B87" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10101,19 +10059,23 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10121,10 +10083,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464083</v>
+        <v>464305</v>
       </c>
       <c r="R87" t="n">
-        <v>7042298</v>
+        <v>7042334</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10157,6 +10119,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10183,10 +10150,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131025520</v>
+        <v>131025477</v>
       </c>
       <c r="B88" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10194,34 +10161,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464027</v>
+        <v>464374</v>
       </c>
       <c r="R88" t="n">
-        <v>7042318</v>
+        <v>7042300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10258,7 +10233,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10269,6 +10244,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10285,10 +10285,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131025496</v>
+        <v>131024475</v>
       </c>
       <c r="B89" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10296,34 +10296,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464485</v>
+        <v>464272</v>
       </c>
       <c r="R89" t="n">
-        <v>7042454</v>
+        <v>7042273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10375,22 +10375,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131025515</v>
+        <v>131024455</v>
       </c>
       <c r="B90" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10398,34 +10398,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464430</v>
+        <v>464454</v>
       </c>
       <c r="R90" t="n">
-        <v>7042344</v>
+        <v>7042523</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10477,19 +10477,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131024475</v>
+        <v>131024466</v>
       </c>
       <c r="B91" t="n">
         <v>57884</v>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464272</v>
+        <v>464319</v>
       </c>
       <c r="R91" t="n">
-        <v>7042273</v>
+        <v>7042385</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10591,10 +10591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131024455</v>
+        <v>131025496</v>
       </c>
       <c r="B92" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10602,34 +10602,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464454</v>
+        <v>464485</v>
       </c>
       <c r="R92" t="n">
-        <v>7042523</v>
+        <v>7042454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10681,22 +10681,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131024466</v>
+        <v>131025515</v>
       </c>
       <c r="B93" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10704,34 +10704,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464319</v>
+        <v>464430</v>
       </c>
       <c r="R93" t="n">
-        <v>7042385</v>
+        <v>7042344</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10783,12 +10783,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11028,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131025507</v>
+        <v>131024452</v>
       </c>
       <c r="B96" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11039,34 +11039,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464297</v>
+        <v>464339</v>
       </c>
       <c r="R96" t="n">
-        <v>7042525</v>
+        <v>7042474</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11118,19 +11118,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131024452</v>
+        <v>131025484</v>
       </c>
       <c r="B97" t="n">
         <v>57884</v>
@@ -11159,16 +11159,24 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464339</v>
+        <v>464099</v>
       </c>
       <c r="R97" t="n">
-        <v>7042474</v>
+        <v>7042646</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11205,7 +11213,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11216,26 +11224,51 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131025484</v>
+        <v>131025507</v>
       </c>
       <c r="B98" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11243,42 +11276,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464099</v>
+        <v>464297</v>
       </c>
       <c r="R98" t="n">
-        <v>7042646</v>
+        <v>7042525</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11315,7 +11340,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på gran.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11326,31 +11351,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131025514</v>
+        <v>131024454</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464434</v>
+        <v>464321</v>
       </c>
       <c r="R2" t="n">
-        <v>7042377</v>
+        <v>7042482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På flera granar vid en lucka.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131024454</v>
+        <v>131025505</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464321</v>
+        <v>464214</v>
       </c>
       <c r="R3" t="n">
-        <v>7042482</v>
+        <v>7042578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131025505</v>
+        <v>131025514</v>
       </c>
       <c r="B4" t="n">
         <v>79244</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464214</v>
+        <v>464434</v>
       </c>
       <c r="R4" t="n">
-        <v>7042578</v>
+        <v>7042377</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På flera granar vid en lucka.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131024469</v>
+        <v>131025513</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464325</v>
+        <v>464484</v>
       </c>
       <c r="R5" t="n">
-        <v>7042323</v>
+        <v>7042425</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025467</v>
+        <v>131025526</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,42 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464403</v>
+        <v>464101</v>
       </c>
       <c r="R6" t="n">
-        <v>7042578</v>
+        <v>7042665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, tydliga på en gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,31 +1169,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1218,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131025513</v>
+        <v>131024469</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,34 +1196,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464484</v>
+        <v>464325</v>
       </c>
       <c r="R7" t="n">
-        <v>7042425</v>
+        <v>7042323</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1260,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131025526</v>
+        <v>131025467</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,34 +1298,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464101</v>
+        <v>464403</v>
       </c>
       <c r="R8" t="n">
-        <v>7042665</v>
+        <v>7042578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1370,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, färska och äldre, tydliga på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1406,6 +1381,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1422,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025502</v>
+        <v>131025506</v>
       </c>
       <c r="B9" t="n">
         <v>79244</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464177</v>
+        <v>464253</v>
       </c>
       <c r="R9" t="n">
-        <v>7042606</v>
+        <v>7042536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025506</v>
+        <v>131025519</v>
       </c>
       <c r="B10" t="n">
         <v>79244</v>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464253</v>
+        <v>464076</v>
       </c>
       <c r="R10" t="n">
-        <v>7042536</v>
+        <v>7042281</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1626,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025519</v>
+        <v>131025512</v>
       </c>
       <c r="B11" t="n">
         <v>79244</v>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464076</v>
+        <v>464451</v>
       </c>
       <c r="R11" t="n">
-        <v>7042281</v>
+        <v>7042487</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,7 +1728,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025512</v>
+        <v>131025518</v>
       </c>
       <c r="B12" t="n">
         <v>79244</v>
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464451</v>
+        <v>464161</v>
       </c>
       <c r="R12" t="n">
-        <v>7042487</v>
+        <v>7042247</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025518</v>
+        <v>131024467</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,34 +1841,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464161</v>
+        <v>464322</v>
       </c>
       <c r="R13" t="n">
-        <v>7042247</v>
+        <v>7042355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,22 +1920,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025494</v>
+        <v>131025463</v>
       </c>
       <c r="B14" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,30 +1943,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464471</v>
+        <v>464211</v>
       </c>
       <c r="R14" t="n">
-        <v>7042462</v>
+        <v>7042581</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2015,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2014,6 +2026,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2030,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025488</v>
+        <v>131025494</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>91829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,42 +2078,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463958</v>
+        <v>464471</v>
       </c>
       <c r="R15" t="n">
-        <v>7042484</v>
+        <v>7042462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2138,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,31 +2149,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2165,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131024467</v>
+        <v>131025502</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,34 +2176,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464322</v>
+        <v>464177</v>
       </c>
       <c r="R16" t="n">
-        <v>7042355</v>
+        <v>7042606</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,22 +2255,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131025463</v>
+        <v>131025488</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464211</v>
+        <v>463958</v>
       </c>
       <c r="R17" t="n">
-        <v>7042581</v>
+        <v>7042484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131025510</v>
+        <v>131024468</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,34 +2413,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464463</v>
+        <v>464332</v>
       </c>
       <c r="R18" t="n">
-        <v>7042542</v>
+        <v>7042344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,22 +2492,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131025525</v>
+        <v>131024458</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,34 +2515,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464067</v>
+        <v>464405</v>
       </c>
       <c r="R19" t="n">
-        <v>7042585</v>
+        <v>7042391</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,19 +2594,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131024468</v>
+        <v>131024464</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464332</v>
+        <v>464337</v>
       </c>
       <c r="R20" t="n">
-        <v>7042344</v>
+        <v>7042380</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024458</v>
+        <v>131025468</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2737,16 +2737,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464405</v>
+        <v>464445</v>
       </c>
       <c r="R21" t="n">
-        <v>7042391</v>
+        <v>7042578</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2791,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2794,26 +2802,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024464</v>
+        <v>131025510</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2821,34 +2854,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464337</v>
+        <v>464463</v>
       </c>
       <c r="R22" t="n">
-        <v>7042380</v>
+        <v>7042542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2918,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2900,22 +2933,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131025468</v>
+        <v>131025525</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,42 +2956,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464445</v>
+        <v>464067</v>
       </c>
       <c r="R23" t="n">
-        <v>7042578</v>
+        <v>7042585</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,31 +3031,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131025528</v>
+        <v>131024476</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464199</v>
+        <v>464255</v>
       </c>
       <c r="R24" t="n">
-        <v>7042793</v>
+        <v>7042273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131024449</v>
+        <v>131025474</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3178,16 +3178,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464183</v>
+        <v>464391</v>
       </c>
       <c r="R25" t="n">
-        <v>7042531</v>
+        <v>7042299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,7 +3232,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,23 +3243,48 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131024476</v>
+        <v>131025470</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3280,16 +3313,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464255</v>
+        <v>464484</v>
       </c>
       <c r="R26" t="n">
-        <v>7042273</v>
+        <v>7042508</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,23 +3378,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131025474</v>
+        <v>131024449</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3382,24 +3448,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464391</v>
+        <v>464183</v>
       </c>
       <c r="R27" t="n">
-        <v>7042299</v>
+        <v>7042531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,7 +3494,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,48 +3505,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131025470</v>
+        <v>131024474</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3517,24 +3550,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464484</v>
+        <v>464280</v>
       </c>
       <c r="R28" t="n">
-        <v>7042508</v>
+        <v>7042322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3596,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3582,48 +3607,23 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131024474</v>
+        <v>131025485</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3652,16 +3652,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464280</v>
+        <v>464186</v>
       </c>
       <c r="R29" t="n">
-        <v>7042322</v>
+        <v>7042779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3706,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,26 +3717,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025485</v>
+        <v>131025528</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3736,42 +3769,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464186</v>
+        <v>464199</v>
       </c>
       <c r="R30" t="n">
-        <v>7042779</v>
+        <v>7042793</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3833,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3819,31 +3844,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3860,10 +3860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131024446</v>
+        <v>131025522</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,42 +3871,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463828</v>
+        <v>463978</v>
       </c>
       <c r="R31" t="n">
-        <v>7042514</v>
+        <v>7042528</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3943,14 +3935,14 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="b">
         <v>0</v>
@@ -3958,22 +3950,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131025464</v>
+        <v>131025509</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3981,42 +3973,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464210</v>
+        <v>464380</v>
       </c>
       <c r="R32" t="n">
-        <v>7042574</v>
+        <v>7042615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4053,7 +4037,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4064,31 +4048,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4105,10 +4064,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131025509</v>
+        <v>131024465</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4116,34 +4075,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464380</v>
+        <v>464328</v>
       </c>
       <c r="R33" t="n">
-        <v>7042615</v>
+        <v>7042367</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4180,7 +4139,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4195,22 +4154,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131025522</v>
+        <v>131024446</v>
       </c>
       <c r="B34" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4218,34 +4177,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463978</v>
+        <v>463828</v>
       </c>
       <c r="R34" t="n">
-        <v>7042528</v>
+        <v>7042514</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4282,14 +4249,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>Gammalt bohål i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4297,19 +4264,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131024465</v>
+        <v>131025464</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4338,16 +4305,24 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464328</v>
+        <v>464210</v>
       </c>
       <c r="R35" t="n">
-        <v>7042367</v>
+        <v>7042574</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4359,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4395,26 +4370,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131025465</v>
+        <v>131025517</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,42 +4422,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464268</v>
+        <v>464199</v>
       </c>
       <c r="R36" t="n">
-        <v>7042527</v>
+        <v>7042210</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,7 +4486,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4505,31 +4497,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4546,10 +4513,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131024448</v>
+        <v>131025527</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,34 +4524,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464165</v>
+        <v>464174</v>
       </c>
       <c r="R37" t="n">
-        <v>7042546</v>
+        <v>7042780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4621,7 +4588,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4636,19 +4603,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025472</v>
+        <v>131025465</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4681,7 +4648,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4691,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464419</v>
+        <v>464268</v>
       </c>
       <c r="R38" t="n">
-        <v>7042316</v>
+        <v>7042527</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4731,7 +4698,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4745,7 +4712,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4783,10 +4750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131025489</v>
+        <v>131024448</v>
       </c>
       <c r="B39" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4794,41 +4761,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464035</v>
+        <v>464165</v>
       </c>
       <c r="R39" t="n">
-        <v>7042354</v>
+        <v>7042546</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4865,7 +4825,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4874,54 +4834,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131025517</v>
+        <v>131024478</v>
       </c>
       <c r="B40" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4929,34 +4863,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464199</v>
+        <v>464232</v>
       </c>
       <c r="R40" t="n">
-        <v>7042210</v>
+        <v>7042762</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,7 +4927,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,22 +4942,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131025527</v>
+        <v>131025472</v>
       </c>
       <c r="B41" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5031,34 +4965,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464174</v>
+        <v>464419</v>
       </c>
       <c r="R41" t="n">
-        <v>7042780</v>
+        <v>7042316</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5095,7 +5037,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5106,6 +5048,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5122,10 +5089,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131024478</v>
+        <v>131025489</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,34 +5100,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464232</v>
+        <v>464035</v>
       </c>
       <c r="R42" t="n">
-        <v>7042762</v>
+        <v>7042354</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,7 +5171,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5206,18 +5180,44 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5665,10 +5665,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025478</v>
+        <v>131025495</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,42 +5676,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464380</v>
+        <v>463986</v>
       </c>
       <c r="R47" t="n">
-        <v>7042301</v>
+        <v>7042522</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5748,7 +5736,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5759,31 +5747,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5800,10 +5763,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025471</v>
+        <v>131024506</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5811,42 +5774,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464444</v>
+        <v>464426</v>
       </c>
       <c r="R48" t="n">
-        <v>7042363</v>
+        <v>7042565</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5881,11 +5832,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5894,53 +5840,23 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025482</v>
+        <v>131025478</v>
       </c>
       <c r="B49" t="n">
         <v>57884</v>
@@ -5973,7 +5889,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -5983,10 +5899,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464034</v>
+        <v>464380</v>
       </c>
       <c r="R49" t="n">
-        <v>7042322</v>
+        <v>7042301</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6023,7 +5939,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6075,10 +5991,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131024506</v>
+        <v>131025471</v>
       </c>
       <c r="B50" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6086,30 +6002,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464426</v>
+        <v>464444</v>
       </c>
       <c r="R50" t="n">
-        <v>7042565</v>
+        <v>7042363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6144,6 +6072,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6152,26 +6085,56 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025495</v>
+        <v>131025482</v>
       </c>
       <c r="B51" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,30 +6142,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463986</v>
+        <v>464034</v>
       </c>
       <c r="R51" t="n">
-        <v>7042522</v>
+        <v>7042322</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6239,7 +6214,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6250,6 +6225,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6470,10 +6470,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131025504</v>
+        <v>131024501</v>
       </c>
       <c r="B54" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,34 +6481,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464204</v>
+        <v>464070</v>
       </c>
       <c r="R54" t="n">
-        <v>7042559</v>
+        <v>7042517</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6543,11 +6543,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6560,22 +6555,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131024463</v>
+        <v>131025504</v>
       </c>
       <c r="B55" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6583,34 +6578,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464371</v>
+        <v>464204</v>
       </c>
       <c r="R55" t="n">
-        <v>7042397</v>
+        <v>7042559</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6647,7 +6642,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6662,19 +6657,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131025483</v>
+        <v>131024463</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -6703,24 +6698,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464021</v>
+        <v>464371</v>
       </c>
       <c r="R56" t="n">
-        <v>7042325</v>
+        <v>7042397</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6757,7 +6744,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6768,48 +6755,23 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131025469</v>
+        <v>131025483</v>
       </c>
       <c r="B57" t="n">
         <v>57884</v>
@@ -6842,7 +6804,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6852,10 +6814,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464464</v>
+        <v>464021</v>
       </c>
       <c r="R57" t="n">
-        <v>7042544</v>
+        <v>7042325</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6892,7 +6854,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6921,12 +6883,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6944,10 +6906,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131024511</v>
+        <v>131025469</v>
       </c>
       <c r="B58" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6955,30 +6917,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>463866</v>
+        <v>464464</v>
       </c>
       <c r="R58" t="n">
-        <v>7042468</v>
+        <v>7042544</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7013,6 +6987,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7021,23 +7000,48 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024510</v>
+        <v>131024507</v>
       </c>
       <c r="B59" t="n">
         <v>91829</v>
@@ -7068,10 +7072,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464031</v>
+        <v>464395</v>
       </c>
       <c r="R59" t="n">
-        <v>7042403</v>
+        <v>7042406</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7130,7 +7134,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131024507</v>
+        <v>131024510</v>
       </c>
       <c r="B60" t="n">
         <v>91829</v>
@@ -7161,10 +7165,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464395</v>
+        <v>464031</v>
       </c>
       <c r="R60" t="n">
-        <v>7042406</v>
+        <v>7042403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7223,10 +7227,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131024501</v>
+        <v>131024511</v>
       </c>
       <c r="B61" t="n">
-        <v>91805</v>
+        <v>91829</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7234,23 +7238,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464070</v>
+        <v>463866</v>
       </c>
       <c r="R61" t="n">
-        <v>7042517</v>
+        <v>7042468</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7320,10 +7320,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131024460</v>
+        <v>131025508</v>
       </c>
       <c r="B62" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,34 +7331,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464385</v>
+        <v>464310</v>
       </c>
       <c r="R62" t="n">
-        <v>7042401</v>
+        <v>7042565</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7395,7 +7395,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7410,19 +7410,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131024450</v>
+        <v>131024460</v>
       </c>
       <c r="B63" t="n">
         <v>57884</v>
@@ -7457,10 +7457,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464273</v>
+        <v>464385</v>
       </c>
       <c r="R63" t="n">
-        <v>7042500</v>
+        <v>7042401</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7524,10 +7524,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131025508</v>
+        <v>131024450</v>
       </c>
       <c r="B64" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7535,34 +7535,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464310</v>
+        <v>464273</v>
       </c>
       <c r="R64" t="n">
-        <v>7042565</v>
+        <v>7042500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7614,22 +7614,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131024509</v>
+        <v>131024456</v>
       </c>
       <c r="B65" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7637,19 +7637,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7657,10 +7661,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464214</v>
+        <v>464439</v>
       </c>
       <c r="R65" t="n">
-        <v>7042282</v>
+        <v>7042505</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7693,6 +7697,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7719,27 +7728,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131024456</v>
+        <v>131024494</v>
       </c>
       <c r="B66" t="n">
-        <v>57884</v>
+        <v>57988</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7747,17 +7756,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464439</v>
+        <v>464304</v>
       </c>
       <c r="R66" t="n">
-        <v>7042505</v>
+        <v>7042379</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7790,11 +7811,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7821,57 +7837,41 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131024494</v>
+        <v>131024509</v>
       </c>
       <c r="B67" t="n">
-        <v>57988</v>
+        <v>91829</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464304</v>
+        <v>464214</v>
       </c>
       <c r="R67" t="n">
-        <v>7042379</v>
+        <v>7042282</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131025516</v>
+        <v>131025479</v>
       </c>
       <c r="B68" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7941,34 +7941,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464319</v>
+        <v>464380</v>
       </c>
       <c r="R68" t="n">
-        <v>7042262</v>
+        <v>7042291</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8005,7 +8013,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8016,6 +8024,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8032,10 +8065,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131025479</v>
+        <v>131025516</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,42 +8076,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464380</v>
+        <v>464319</v>
       </c>
       <c r="R69" t="n">
-        <v>7042291</v>
+        <v>7042262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +8140,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8126,31 +8151,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8506,10 +8506,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131024453</v>
+        <v>131025521</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8517,34 +8517,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464327</v>
+        <v>464007</v>
       </c>
       <c r="R73" t="n">
-        <v>7042477</v>
+        <v>7042409</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,19 +8596,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131024451</v>
+        <v>131024453</v>
       </c>
       <c r="B74" t="n">
         <v>57884</v>
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464275</v>
+        <v>464327</v>
       </c>
       <c r="R74" t="n">
-        <v>7042455</v>
+        <v>7042477</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131025480</v>
+        <v>131024451</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8739,24 +8739,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464378</v>
+        <v>464275</v>
       </c>
       <c r="R75" t="n">
-        <v>7042302</v>
+        <v>7042455</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8793,7 +8785,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8804,51 +8796,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131025521</v>
+        <v>131025480</v>
       </c>
       <c r="B76" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8856,34 +8823,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464007</v>
+        <v>464378</v>
       </c>
       <c r="R76" t="n">
-        <v>7042409</v>
+        <v>7042302</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8920,7 +8895,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8931,6 +8906,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8947,10 +8947,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131024470</v>
+        <v>131025492</v>
       </c>
       <c r="B77" t="n">
-        <v>57884</v>
+        <v>91805</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,34 +8958,41 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464325</v>
+        <v>464400</v>
       </c>
       <c r="R77" t="n">
-        <v>7042334</v>
+        <v>7042294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9022,7 +9029,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9031,28 +9038,54 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131024461</v>
+        <v>131025490</v>
       </c>
       <c r="B78" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9060,34 +9093,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464377</v>
+        <v>463994</v>
       </c>
       <c r="R78" t="n">
-        <v>7042402</v>
+        <v>7042378</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9124,7 +9164,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9133,25 +9173,51 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131025503</v>
+        <v>131025523</v>
       </c>
       <c r="B79" t="n">
         <v>79244</v>
@@ -9186,10 +9252,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464158</v>
+        <v>463999</v>
       </c>
       <c r="R79" t="n">
-        <v>7042548</v>
+        <v>7042559</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9226,7 +9292,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9253,10 +9319,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131025492</v>
+        <v>131025503</v>
       </c>
       <c r="B80" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9264,41 +9330,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464400</v>
+        <v>464158</v>
       </c>
       <c r="R80" t="n">
-        <v>7042294</v>
+        <v>7042548</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9335,7 +9394,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9344,34 +9403,8 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9388,10 +9421,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131025490</v>
+        <v>131024470</v>
       </c>
       <c r="B81" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9399,41 +9432,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>463994</v>
+        <v>464325</v>
       </c>
       <c r="R81" t="n">
-        <v>7042378</v>
+        <v>7042334</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9470,7 +9496,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9479,54 +9505,28 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131025523</v>
+        <v>131024461</v>
       </c>
       <c r="B82" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9534,34 +9534,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>463999</v>
+        <v>464377</v>
       </c>
       <c r="R82" t="n">
-        <v>7042559</v>
+        <v>7042402</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9613,22 +9613,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131024505</v>
+        <v>131025520</v>
       </c>
       <c r="B83" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9636,30 +9636,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464276</v>
+        <v>464027</v>
       </c>
       <c r="R83" t="n">
-        <v>7042457</v>
+        <v>7042318</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9694,6 +9698,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9706,22 +9715,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131024508</v>
+        <v>131025475</v>
       </c>
       <c r="B84" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9729,30 +9738,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464083</v>
+        <v>464393</v>
       </c>
       <c r="R84" t="n">
-        <v>7042298</v>
+        <v>7042284</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9787,6 +9808,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9795,26 +9821,51 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131025520</v>
+        <v>131024473</v>
       </c>
       <c r="B85" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9822,34 +9873,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464027</v>
+        <v>464305</v>
       </c>
       <c r="R85" t="n">
-        <v>7042318</v>
+        <v>7042334</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9886,7 +9937,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9901,19 +9952,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131025475</v>
+        <v>131025477</v>
       </c>
       <c r="B86" t="n">
         <v>57884</v>
@@ -9956,10 +10007,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464393</v>
+        <v>464374</v>
       </c>
       <c r="R86" t="n">
-        <v>7042284</v>
+        <v>7042300</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,7 +10047,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10048,10 +10099,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131024473</v>
+        <v>131024508</v>
       </c>
       <c r="B87" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10059,23 +10110,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10083,10 +10130,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464305</v>
+        <v>464083</v>
       </c>
       <c r="R87" t="n">
-        <v>7042334</v>
+        <v>7042298</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10119,11 +10166,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10150,10 +10192,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131025477</v>
+        <v>131024505</v>
       </c>
       <c r="B88" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10161,42 +10203,30 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464374</v>
+        <v>464276</v>
       </c>
       <c r="R88" t="n">
-        <v>7042300</v>
+        <v>7042457</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10231,11 +10261,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10244,51 +10269,26 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131024475</v>
+        <v>131025496</v>
       </c>
       <c r="B89" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10296,34 +10296,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464272</v>
+        <v>464485</v>
       </c>
       <c r="R89" t="n">
-        <v>7042273</v>
+        <v>7042454</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10375,22 +10375,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131024455</v>
+        <v>131025515</v>
       </c>
       <c r="B90" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10398,34 +10398,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464454</v>
+        <v>464430</v>
       </c>
       <c r="R90" t="n">
-        <v>7042523</v>
+        <v>7042344</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10477,19 +10477,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131024466</v>
+        <v>131024475</v>
       </c>
       <c r="B91" t="n">
         <v>57884</v>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464319</v>
+        <v>464272</v>
       </c>
       <c r="R91" t="n">
-        <v>7042385</v>
+        <v>7042273</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10591,10 +10591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131025496</v>
+        <v>131024455</v>
       </c>
       <c r="B92" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10602,34 +10602,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464485</v>
+        <v>464454</v>
       </c>
       <c r="R92" t="n">
-        <v>7042454</v>
+        <v>7042523</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10681,22 +10681,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131025515</v>
+        <v>131024466</v>
       </c>
       <c r="B93" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10704,34 +10704,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464430</v>
+        <v>464319</v>
       </c>
       <c r="R93" t="n">
-        <v>7042344</v>
+        <v>7042385</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10783,12 +10783,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025506</v>
+        <v>131025494</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,23 +1433,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1457,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464253</v>
+        <v>464471</v>
       </c>
       <c r="R9" t="n">
-        <v>7042536</v>
+        <v>7042462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1493,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025519</v>
+        <v>131025506</v>
       </c>
       <c r="B10" t="n">
         <v>79244</v>
@@ -1559,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464076</v>
+        <v>464253</v>
       </c>
       <c r="R10" t="n">
-        <v>7042281</v>
+        <v>7042536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1626,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025512</v>
+        <v>131025502</v>
       </c>
       <c r="B11" t="n">
         <v>79244</v>
@@ -1661,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464451</v>
+        <v>464177</v>
       </c>
       <c r="R11" t="n">
-        <v>7042487</v>
+        <v>7042606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,7 +1724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025518</v>
+        <v>131025519</v>
       </c>
       <c r="B12" t="n">
         <v>79244</v>
@@ -1763,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464161</v>
+        <v>464076</v>
       </c>
       <c r="R12" t="n">
-        <v>7042247</v>
+        <v>7042281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,7 +1799,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131024467</v>
+        <v>131025512</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,34 +1837,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464322</v>
+        <v>464451</v>
       </c>
       <c r="R13" t="n">
-        <v>7042355</v>
+        <v>7042487</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1901,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,22 +1916,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025463</v>
+        <v>131025518</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1943,42 +1939,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464211</v>
+        <v>464161</v>
       </c>
       <c r="R14" t="n">
-        <v>7042581</v>
+        <v>7042247</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,31 +2014,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2067,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025494</v>
+        <v>131024467</v>
       </c>
       <c r="B15" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,30 +2041,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464471</v>
+        <v>464322</v>
       </c>
       <c r="R15" t="n">
-        <v>7042462</v>
+        <v>7042355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2105,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,22 +2120,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131025502</v>
+        <v>131025463</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,34 +2143,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464177</v>
+        <v>464211</v>
       </c>
       <c r="R16" t="n">
-        <v>7042606</v>
+        <v>7042581</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,7 +2215,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2251,6 +2226,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131024468</v>
+        <v>131025468</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2431,16 +2431,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464332</v>
+        <v>464445</v>
       </c>
       <c r="R18" t="n">
-        <v>7042344</v>
+        <v>7042578</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2485,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,26 +2496,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131024458</v>
+        <v>131025510</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,34 +2548,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464405</v>
+        <v>464463</v>
       </c>
       <c r="R19" t="n">
-        <v>7042391</v>
+        <v>7042542</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2612,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2627,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131024464</v>
+        <v>131025525</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2617,34 +2650,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464337</v>
+        <v>464067</v>
       </c>
       <c r="R20" t="n">
-        <v>7042380</v>
+        <v>7042585</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2714,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,19 +2729,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131025468</v>
+        <v>131024468</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2737,24 +2770,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464445</v>
+        <v>464332</v>
       </c>
       <c r="R21" t="n">
-        <v>7042578</v>
+        <v>7042344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,7 +2816,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2802,51 +2827,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131025510</v>
+        <v>131024458</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2854,34 +2854,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464463</v>
+        <v>464405</v>
       </c>
       <c r="R22" t="n">
-        <v>7042542</v>
+        <v>7042391</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2933,22 +2933,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131025525</v>
+        <v>131024464</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,34 +2956,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464067</v>
+        <v>464337</v>
       </c>
       <c r="R23" t="n">
-        <v>7042585</v>
+        <v>7042380</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3035,22 +3035,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131024476</v>
+        <v>131025528</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464255</v>
+        <v>464199</v>
       </c>
       <c r="R24" t="n">
-        <v>7042273</v>
+        <v>7042793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131025474</v>
+        <v>131025485</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464391</v>
+        <v>464186</v>
       </c>
       <c r="R25" t="n">
-        <v>7042299</v>
+        <v>7042779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,7 +3419,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131024449</v>
+        <v>131025474</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3448,16 +3448,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464183</v>
+        <v>464391</v>
       </c>
       <c r="R27" t="n">
-        <v>7042531</v>
+        <v>7042299</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3494,7 +3502,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,23 +3513,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024474</v>
+        <v>131024476</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3556,10 +3589,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464280</v>
+        <v>464255</v>
       </c>
       <c r="R28" t="n">
-        <v>7042322</v>
+        <v>7042273</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3623,7 +3656,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131025485</v>
+        <v>131024449</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3652,24 +3685,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464186</v>
+        <v>464183</v>
       </c>
       <c r="R29" t="n">
-        <v>7042779</v>
+        <v>7042531</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3731,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3717,51 +3742,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025528</v>
+        <v>131024474</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,34 +3769,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464199</v>
+        <v>464280</v>
       </c>
       <c r="R30" t="n">
-        <v>7042793</v>
+        <v>7042322</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,22 +3848,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025522</v>
+        <v>131025464</v>
       </c>
       <c r="B31" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,34 +3871,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463978</v>
+        <v>464210</v>
       </c>
       <c r="R31" t="n">
-        <v>7042528</v>
+        <v>7042574</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3943,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3946,6 +3954,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4064,10 +4097,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131024465</v>
+        <v>131025522</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4075,34 +4108,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464328</v>
+        <v>463978</v>
       </c>
       <c r="R33" t="n">
-        <v>7042367</v>
+        <v>7042528</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,7 +4172,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4154,19 +4187,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131024446</v>
+        <v>131024465</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4195,24 +4228,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463828</v>
+        <v>464328</v>
       </c>
       <c r="R34" t="n">
-        <v>7042514</v>
+        <v>7042367</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,14 +4274,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4276,7 +4301,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131025464</v>
+        <v>131024446</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4309,20 +4334,20 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464210</v>
+        <v>463828</v>
       </c>
       <c r="R35" t="n">
-        <v>7042574</v>
+        <v>7042514</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,62 +4384,37 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Gammalt bohål i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131025517</v>
+        <v>131024448</v>
       </c>
       <c r="B36" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,34 +4422,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464199</v>
+        <v>464165</v>
       </c>
       <c r="R36" t="n">
-        <v>7042210</v>
+        <v>7042546</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4501,22 +4501,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131025527</v>
+        <v>131024478</v>
       </c>
       <c r="B37" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,34 +4524,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464174</v>
+        <v>464232</v>
       </c>
       <c r="R37" t="n">
-        <v>7042780</v>
+        <v>7042762</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,19 +4603,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025465</v>
+        <v>131025472</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4648,7 +4648,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464268</v>
+        <v>464419</v>
       </c>
       <c r="R38" t="n">
-        <v>7042527</v>
+        <v>7042316</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4750,10 +4750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131024448</v>
+        <v>131025489</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,34 +4761,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464165</v>
+        <v>464035</v>
       </c>
       <c r="R39" t="n">
-        <v>7042546</v>
+        <v>7042354</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4825,7 +4832,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4834,28 +4841,54 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131024478</v>
+        <v>131025517</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4863,34 +4896,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464232</v>
+        <v>464199</v>
       </c>
       <c r="R40" t="n">
-        <v>7042762</v>
+        <v>7042210</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4927,7 +4960,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4942,22 +4975,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131025472</v>
+        <v>131025527</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4965,42 +4998,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464419</v>
+        <v>464174</v>
       </c>
       <c r="R41" t="n">
-        <v>7042316</v>
+        <v>7042780</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5037,7 +5062,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5048,31 +5073,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5089,10 +5089,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025489</v>
+        <v>131025465</v>
       </c>
       <c r="B42" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,28 +5100,29 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5131,10 +5132,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464035</v>
+        <v>464268</v>
       </c>
       <c r="R42" t="n">
-        <v>7042354</v>
+        <v>7042527</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5171,7 +5172,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5180,33 +5181,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131025466</v>
+        <v>131024459</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5457,24 +5457,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464389</v>
+        <v>464397</v>
       </c>
       <c r="R45" t="n">
-        <v>7042585</v>
+        <v>7042399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5511,7 +5503,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5522,48 +5514,23 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131024459</v>
+        <v>131025466</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5592,16 +5559,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464397</v>
+        <v>464389</v>
       </c>
       <c r="R46" t="n">
-        <v>7042399</v>
+        <v>7042585</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5638,7 +5613,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5649,26 +5624,51 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025495</v>
+        <v>131025524</v>
       </c>
       <c r="B47" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,19 +5676,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5696,10 +5700,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463986</v>
+        <v>464041</v>
       </c>
       <c r="R47" t="n">
-        <v>7042522</v>
+        <v>7042631</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5736,7 +5740,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5763,10 +5767,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131024506</v>
+        <v>131025511</v>
       </c>
       <c r="B48" t="n">
-        <v>91829</v>
+        <v>79244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,30 +5778,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464426</v>
+        <v>464483</v>
       </c>
       <c r="R48" t="n">
-        <v>7042565</v>
+        <v>7042518</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5832,6 +5840,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5844,22 +5857,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025478</v>
+        <v>131024506</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5867,42 +5880,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464380</v>
+        <v>464426</v>
       </c>
       <c r="R49" t="n">
-        <v>7042301</v>
+        <v>7042565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5937,11 +5938,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5950,51 +5946,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025471</v>
+        <v>131025495</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6002,42 +5973,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464444</v>
+        <v>463986</v>
       </c>
       <c r="R50" t="n">
-        <v>7042363</v>
+        <v>7042522</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6074,7 +6033,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6085,36 +6044,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6266,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025524</v>
+        <v>131025471</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,34 +6206,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464041</v>
+        <v>464444</v>
       </c>
       <c r="R52" t="n">
-        <v>7042631</v>
+        <v>7042363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6341,7 +6278,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6352,6 +6289,36 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6368,10 +6335,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025511</v>
+        <v>131025478</v>
       </c>
       <c r="B53" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6379,34 +6346,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464483</v>
+        <v>464380</v>
       </c>
       <c r="R53" t="n">
-        <v>7042518</v>
+        <v>7042301</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6443,7 +6418,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6454,6 +6429,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6669,10 +6669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024463</v>
+        <v>131024511</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6680,23 +6680,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6704,10 +6700,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464371</v>
+        <v>463866</v>
       </c>
       <c r="R56" t="n">
-        <v>7042397</v>
+        <v>7042468</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6740,11 +6736,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6771,10 +6762,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131025483</v>
+        <v>131024510</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,42 +6773,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464021</v>
+        <v>464031</v>
       </c>
       <c r="R57" t="n">
-        <v>7042325</v>
+        <v>7042403</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6852,11 +6831,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6865,51 +6839,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131025469</v>
+        <v>131024507</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,42 +6866,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464464</v>
+        <v>464395</v>
       </c>
       <c r="R58" t="n">
-        <v>7042544</v>
+        <v>7042406</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6987,11 +6924,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7000,51 +6932,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024507</v>
+        <v>131024463</v>
       </c>
       <c r="B59" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,19 +6959,23 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7072,10 +6983,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464395</v>
+        <v>464371</v>
       </c>
       <c r="R59" t="n">
-        <v>7042406</v>
+        <v>7042397</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7108,6 +7019,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7134,10 +7050,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131024510</v>
+        <v>131025483</v>
       </c>
       <c r="B60" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7145,30 +7061,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464031</v>
+        <v>464021</v>
       </c>
       <c r="R60" t="n">
-        <v>7042403</v>
+        <v>7042325</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7203,6 +7131,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7211,26 +7144,51 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131024511</v>
+        <v>131025469</v>
       </c>
       <c r="B61" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7238,30 +7196,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>463866</v>
+        <v>464464</v>
       </c>
       <c r="R61" t="n">
-        <v>7042468</v>
+        <v>7042544</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7296,6 +7266,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7304,16 +7279,41 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131025479</v>
+        <v>131025516</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7941,42 +7941,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464380</v>
+        <v>464319</v>
       </c>
       <c r="R68" t="n">
-        <v>7042291</v>
+        <v>7042262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8013,7 +8005,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8024,31 +8016,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8065,10 +8032,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131025516</v>
+        <v>131025479</v>
       </c>
       <c r="B69" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8076,34 +8043,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464319</v>
+        <v>464380</v>
       </c>
       <c r="R69" t="n">
-        <v>7042262</v>
+        <v>7042291</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8140,7 +8115,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8151,6 +8126,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8167,7 +8167,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131024472</v>
+        <v>131025481</v>
       </c>
       <c r="B70" t="n">
         <v>57884</v>
@@ -8196,16 +8196,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464305</v>
+        <v>464066</v>
       </c>
       <c r="R70" t="n">
-        <v>7042324</v>
+        <v>7042307</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8242,7 +8250,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8253,23 +8261,48 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131024477</v>
+        <v>131024472</v>
       </c>
       <c r="B71" t="n">
         <v>57884</v>
@@ -8304,10 +8337,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464028</v>
+        <v>464305</v>
       </c>
       <c r="R71" t="n">
-        <v>7042322</v>
+        <v>7042324</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8371,7 +8404,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131025481</v>
+        <v>131024477</v>
       </c>
       <c r="B72" t="n">
         <v>57884</v>
@@ -8400,24 +8433,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464066</v>
+        <v>464028</v>
       </c>
       <c r="R72" t="n">
-        <v>7042307</v>
+        <v>7042322</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8454,7 +8479,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8465,41 +8490,16 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131025492</v>
+        <v>131025490</v>
       </c>
       <c r="B77" t="n">
-        <v>91805</v>
+        <v>80350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,28 +8958,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464400</v>
+        <v>463994</v>
       </c>
       <c r="R77" t="n">
-        <v>7042294</v>
+        <v>7042378</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9049,22 +9049,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131025490</v>
+        <v>131025492</v>
       </c>
       <c r="B78" t="n">
-        <v>80350</v>
+        <v>91805</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,28 +9093,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>463994</v>
+        <v>464400</v>
       </c>
       <c r="R78" t="n">
-        <v>7042378</v>
+        <v>7042294</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9184,22 +9184,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9727,7 +9727,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131025475</v>
+        <v>131024473</v>
       </c>
       <c r="B84" t="n">
         <v>57884</v>
@@ -9756,24 +9756,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464393</v>
+        <v>464305</v>
       </c>
       <c r="R84" t="n">
-        <v>7042284</v>
+        <v>7042334</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9810,7 +9802,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9821,51 +9813,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131024473</v>
+        <v>131024505</v>
       </c>
       <c r="B85" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9873,23 +9840,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9897,10 +9860,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464305</v>
+        <v>464276</v>
       </c>
       <c r="R85" t="n">
-        <v>7042334</v>
+        <v>7042457</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9933,11 +9896,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9964,10 +9922,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131025477</v>
+        <v>131024508</v>
       </c>
       <c r="B86" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9975,42 +9933,30 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464374</v>
+        <v>464083</v>
       </c>
       <c r="R86" t="n">
-        <v>7042300</v>
+        <v>7042298</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10045,11 +9991,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10058,51 +9999,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131024508</v>
+        <v>131025477</v>
       </c>
       <c r="B87" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10110,30 +10026,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464083</v>
+        <v>464374</v>
       </c>
       <c r="R87" t="n">
-        <v>7042298</v>
+        <v>7042300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10168,6 +10096,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10176,26 +10109,51 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131024505</v>
+        <v>131025475</v>
       </c>
       <c r="B88" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10203,30 +10161,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464276</v>
+        <v>464393</v>
       </c>
       <c r="R88" t="n">
-        <v>7042457</v>
+        <v>7042284</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10261,6 +10231,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10269,16 +10244,41 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>131025505</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131025514</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131025513</v>
+        <v>131025526</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464484</v>
+        <v>464101</v>
       </c>
       <c r="R5" t="n">
-        <v>7042425</v>
+        <v>7042665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025526</v>
+        <v>131025513</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464101</v>
+        <v>464484</v>
       </c>
       <c r="R6" t="n">
-        <v>7042665</v>
+        <v>7042425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1425,7 +1425,7 @@
         <v>131025494</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025506</v>
+        <v>131025519</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464253</v>
+        <v>464076</v>
       </c>
       <c r="R10" t="n">
-        <v>7042536</v>
+        <v>7042281</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,7 +1625,7 @@
         <v>131025502</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025519</v>
+        <v>131025506</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464076</v>
+        <v>464253</v>
       </c>
       <c r="R12" t="n">
-        <v>7042281</v>
+        <v>7042536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,7 +1829,7 @@
         <v>131025512</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>131025518</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131024467</v>
+        <v>131025488</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2059,16 +2059,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464322</v>
+        <v>463958</v>
       </c>
       <c r="R15" t="n">
-        <v>7042355</v>
+        <v>7042484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,7 +2113,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,23 +2124,48 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131025463</v>
+        <v>131024467</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2161,24 +2194,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464211</v>
+        <v>464322</v>
       </c>
       <c r="R16" t="n">
-        <v>7042581</v>
+        <v>7042355</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2240,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2226,51 +2251,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131025488</v>
+        <v>131025463</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463958</v>
+        <v>464211</v>
       </c>
       <c r="R17" t="n">
-        <v>7042484</v>
+        <v>7042581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131025468</v>
+        <v>131025525</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,42 +2413,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464445</v>
+        <v>464067</v>
       </c>
       <c r="R18" t="n">
-        <v>7042578</v>
+        <v>7042585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,7 +2477,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2496,31 +2488,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2540,7 +2507,7 @@
         <v>131025510</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2639,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131025525</v>
+        <v>131024468</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,34 +2617,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464067</v>
+        <v>464332</v>
       </c>
       <c r="R20" t="n">
-        <v>7042585</v>
+        <v>7042344</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2714,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,19 +2696,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024468</v>
+        <v>131024458</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2776,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464332</v>
+        <v>464405</v>
       </c>
       <c r="R21" t="n">
-        <v>7042344</v>
+        <v>7042391</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2816,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2843,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024458</v>
+        <v>131024464</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -2878,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464405</v>
+        <v>464337</v>
       </c>
       <c r="R22" t="n">
-        <v>7042391</v>
+        <v>7042380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2945,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131024464</v>
+        <v>131025468</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2974,16 +2941,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464337</v>
+        <v>464445</v>
       </c>
       <c r="R23" t="n">
-        <v>7042380</v>
+        <v>7042578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +2995,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,26 +3006,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131025528</v>
+        <v>131024476</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464199</v>
+        <v>464255</v>
       </c>
       <c r="R24" t="n">
-        <v>7042793</v>
+        <v>7042273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131025485</v>
+        <v>131025474</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464186</v>
+        <v>464391</v>
       </c>
       <c r="R25" t="n">
-        <v>7042779</v>
+        <v>7042299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,7 +3419,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131025474</v>
+        <v>131024449</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3448,24 +3448,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464391</v>
+        <v>464183</v>
       </c>
       <c r="R27" t="n">
-        <v>7042299</v>
+        <v>7042531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3502,7 +3494,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3513,48 +3505,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024476</v>
+        <v>131024474</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3589,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464255</v>
+        <v>464280</v>
       </c>
       <c r="R28" t="n">
-        <v>7042273</v>
+        <v>7042322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3656,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131024449</v>
+        <v>131025485</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3685,16 +3652,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464183</v>
+        <v>464186</v>
       </c>
       <c r="R29" t="n">
-        <v>7042531</v>
+        <v>7042779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3731,7 +3706,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3742,26 +3717,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131024474</v>
+        <v>131025528</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,34 +3769,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464280</v>
+        <v>464199</v>
       </c>
       <c r="R30" t="n">
-        <v>7042322</v>
+        <v>7042793</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3848,22 +3848,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025464</v>
+        <v>131025522</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3871,42 +3871,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464210</v>
+        <v>463978</v>
       </c>
       <c r="R31" t="n">
-        <v>7042574</v>
+        <v>7042528</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3943,7 +3935,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3954,31 +3946,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -3998,7 +3965,7 @@
         <v>131025509</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,10 +4064,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131025522</v>
+        <v>131024465</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,34 +4075,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>463978</v>
+        <v>464328</v>
       </c>
       <c r="R33" t="n">
-        <v>7042528</v>
+        <v>7042367</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4172,7 +4139,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4187,19 +4154,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131024465</v>
+        <v>131024446</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -4228,16 +4195,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464328</v>
+        <v>463828</v>
       </c>
       <c r="R34" t="n">
-        <v>7042367</v>
+        <v>7042514</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4274,14 +4249,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4301,7 +4276,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131024446</v>
+        <v>131025464</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4334,20 +4309,20 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>463828</v>
+        <v>464210</v>
       </c>
       <c r="R35" t="n">
-        <v>7042514</v>
+        <v>7042574</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,34 +4359,59 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131024448</v>
+        <v>131025465</v>
       </c>
       <c r="B36" t="n">
         <v>57884</v>
@@ -4440,16 +4440,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464165</v>
+        <v>464268</v>
       </c>
       <c r="R36" t="n">
-        <v>7042546</v>
+        <v>7042527</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4486,7 +4494,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4497,23 +4505,48 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131024478</v>
+        <v>131024448</v>
       </c>
       <c r="B37" t="n">
         <v>57884</v>
@@ -4548,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464232</v>
+        <v>464165</v>
       </c>
       <c r="R37" t="n">
-        <v>7042762</v>
+        <v>7042546</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4615,7 +4648,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025472</v>
+        <v>131024478</v>
       </c>
       <c r="B38" t="n">
         <v>57884</v>
@@ -4644,24 +4677,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464419</v>
+        <v>464232</v>
       </c>
       <c r="R38" t="n">
-        <v>7042316</v>
+        <v>7042762</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4698,7 +4723,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4709,51 +4734,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131025489</v>
+        <v>131025472</v>
       </c>
       <c r="B39" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4761,28 +4761,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4792,10 +4793,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464035</v>
+        <v>464419</v>
       </c>
       <c r="R39" t="n">
-        <v>7042354</v>
+        <v>7042316</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4832,7 +4833,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4841,7 +4842,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4852,22 +4852,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4888,7 +4888,7 @@
         <v>131025517</v>
       </c>
       <c r="B40" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131025527</v>
+        <v>131025489</v>
       </c>
       <c r="B41" t="n">
-        <v>79244</v>
+        <v>80351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4998,34 +4998,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464174</v>
+        <v>464035</v>
       </c>
       <c r="R41" t="n">
-        <v>7042780</v>
+        <v>7042354</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5062,7 +5069,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5071,8 +5078,34 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5089,10 +5122,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025465</v>
+        <v>131025527</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,42 +5133,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464268</v>
+        <v>464174</v>
       </c>
       <c r="R42" t="n">
-        <v>7042527</v>
+        <v>7042780</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5172,7 +5197,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5183,31 +5208,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5428,7 +5428,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131024459</v>
+        <v>131025466</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5457,16 +5457,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464397</v>
+        <v>464389</v>
       </c>
       <c r="R45" t="n">
-        <v>7042399</v>
+        <v>7042585</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5511,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5514,23 +5522,48 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131025466</v>
+        <v>131024459</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5559,24 +5592,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464389</v>
+        <v>464397</v>
       </c>
       <c r="R46" t="n">
-        <v>7042585</v>
+        <v>7042399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5613,7 +5638,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,51 +5649,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025524</v>
+        <v>131025495</v>
       </c>
       <c r="B47" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,23 +5676,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5700,10 +5696,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464041</v>
+        <v>463986</v>
       </c>
       <c r="R47" t="n">
-        <v>7042631</v>
+        <v>7042522</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5740,7 +5736,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5767,10 +5763,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025511</v>
+        <v>131025524</v>
       </c>
       <c r="B48" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5802,10 +5798,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464483</v>
+        <v>464041</v>
       </c>
       <c r="R48" t="n">
-        <v>7042518</v>
+        <v>7042631</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,7 +5838,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5872,7 +5868,7 @@
         <v>131024506</v>
       </c>
       <c r="B49" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5962,10 +5958,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025495</v>
+        <v>131025511</v>
       </c>
       <c r="B50" t="n">
-        <v>91829</v>
+        <v>79245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5973,19 +5969,23 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5993,10 +5993,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>463986</v>
+        <v>464483</v>
       </c>
       <c r="R50" t="n">
-        <v>7042522</v>
+        <v>7042518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6060,7 +6060,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025482</v>
+        <v>131025478</v>
       </c>
       <c r="B51" t="n">
         <v>57884</v>
@@ -6093,7 +6093,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464034</v>
+        <v>464380</v>
       </c>
       <c r="R51" t="n">
-        <v>7042322</v>
+        <v>7042301</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6335,7 +6335,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025478</v>
+        <v>131025482</v>
       </c>
       <c r="B53" t="n">
         <v>57884</v>
@@ -6368,7 +6368,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464380</v>
+        <v>464034</v>
       </c>
       <c r="R53" t="n">
-        <v>7042301</v>
+        <v>7042322</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,7 +6473,7 @@
         <v>131024501</v>
       </c>
       <c r="B54" t="n">
-        <v>91805</v>
+        <v>91806</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>131025504</v>
       </c>
       <c r="B55" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024511</v>
+        <v>131024463</v>
       </c>
       <c r="B56" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6680,19 +6680,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6700,10 +6704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463866</v>
+        <v>464371</v>
       </c>
       <c r="R56" t="n">
-        <v>7042468</v>
+        <v>7042397</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6736,6 +6740,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6762,10 +6771,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024510</v>
+        <v>131025483</v>
       </c>
       <c r="B57" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6773,30 +6782,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464031</v>
+        <v>464021</v>
       </c>
       <c r="R57" t="n">
-        <v>7042403</v>
+        <v>7042325</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6831,6 +6852,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6839,26 +6865,51 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131024507</v>
+        <v>131025469</v>
       </c>
       <c r="B58" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6866,30 +6917,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464395</v>
+        <v>464464</v>
       </c>
       <c r="R58" t="n">
-        <v>7042406</v>
+        <v>7042544</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6924,6 +6987,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6932,26 +7000,51 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024463</v>
+        <v>131024511</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,23 +7052,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6983,10 +7072,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464371</v>
+        <v>463866</v>
       </c>
       <c r="R59" t="n">
-        <v>7042397</v>
+        <v>7042468</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7019,11 +7108,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7050,10 +7134,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131025483</v>
+        <v>131024510</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7061,42 +7145,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464021</v>
+        <v>464031</v>
       </c>
       <c r="R60" t="n">
-        <v>7042325</v>
+        <v>7042403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7131,11 +7203,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7144,51 +7211,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131025469</v>
+        <v>131024507</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7196,42 +7238,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464464</v>
+        <v>464395</v>
       </c>
       <c r="R61" t="n">
-        <v>7042544</v>
+        <v>7042406</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7266,11 +7296,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7279,41 +7304,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
         <v>131025508</v>
       </c>
       <c r="B62" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>131024509</v>
       </c>
       <c r="B67" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>131025516</v>
       </c>
       <c r="B68" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131025481</v>
+        <v>131024472</v>
       </c>
       <c r="B70" t="n">
         <v>57884</v>
@@ -8196,24 +8196,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464066</v>
+        <v>464305</v>
       </c>
       <c r="R70" t="n">
-        <v>7042307</v>
+        <v>7042324</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8250,7 +8242,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8261,48 +8253,23 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131024472</v>
+        <v>131024477</v>
       </c>
       <c r="B71" t="n">
         <v>57884</v>
@@ -8337,10 +8304,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464305</v>
+        <v>464028</v>
       </c>
       <c r="R71" t="n">
-        <v>7042324</v>
+        <v>7042322</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8404,7 +8371,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131024477</v>
+        <v>131025481</v>
       </c>
       <c r="B72" t="n">
         <v>57884</v>
@@ -8433,16 +8400,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464028</v>
+        <v>464066</v>
       </c>
       <c r="R72" t="n">
-        <v>7042322</v>
+        <v>7042307</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8479,7 +8454,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8490,16 +8465,41 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8509,7 +8509,7 @@
         <v>131025521</v>
       </c>
       <c r="B73" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>131025490</v>
       </c>
       <c r="B77" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131025492</v>
+        <v>131025523</v>
       </c>
       <c r="B78" t="n">
-        <v>91805</v>
+        <v>79245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,41 +9093,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464400</v>
+        <v>463999</v>
       </c>
       <c r="R78" t="n">
-        <v>7042294</v>
+        <v>7042559</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9164,7 +9157,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9173,34 +9166,8 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9217,10 +9184,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131025523</v>
+        <v>131025503</v>
       </c>
       <c r="B79" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9252,10 +9219,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>463999</v>
+        <v>464158</v>
       </c>
       <c r="R79" t="n">
-        <v>7042559</v>
+        <v>7042548</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9292,7 +9259,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9319,10 +9286,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131025503</v>
+        <v>131024470</v>
       </c>
       <c r="B80" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9330,34 +9297,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464158</v>
+        <v>464325</v>
       </c>
       <c r="R80" t="n">
-        <v>7042548</v>
+        <v>7042334</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9394,7 +9361,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9409,19 +9376,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131024470</v>
+        <v>131024461</v>
       </c>
       <c r="B81" t="n">
         <v>57884</v>
@@ -9456,10 +9423,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464325</v>
+        <v>464377</v>
       </c>
       <c r="R81" t="n">
-        <v>7042334</v>
+        <v>7042402</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9496,7 +9463,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9523,10 +9490,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131024461</v>
+        <v>131025492</v>
       </c>
       <c r="B82" t="n">
-        <v>57884</v>
+        <v>91806</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9534,34 +9501,41 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464377</v>
+        <v>464400</v>
       </c>
       <c r="R82" t="n">
-        <v>7042402</v>
+        <v>7042294</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9598,7 +9572,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9607,18 +9581,44 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9628,7 +9628,7 @@
         <v>131025520</v>
       </c>
       <c r="B83" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9727,10 +9727,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131024473</v>
+        <v>131024505</v>
       </c>
       <c r="B84" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9738,23 +9738,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9762,10 +9758,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464305</v>
+        <v>464276</v>
       </c>
       <c r="R84" t="n">
-        <v>7042334</v>
+        <v>7042457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9798,11 +9794,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9829,10 +9820,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131024505</v>
+        <v>131024508</v>
       </c>
       <c r="B85" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9860,10 +9851,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464276</v>
+        <v>464083</v>
       </c>
       <c r="R85" t="n">
-        <v>7042457</v>
+        <v>7042298</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9922,10 +9913,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131024508</v>
+        <v>131025475</v>
       </c>
       <c r="B86" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,30 +9924,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464083</v>
+        <v>464393</v>
       </c>
       <c r="R86" t="n">
-        <v>7042298</v>
+        <v>7042284</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9991,6 +9994,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9999,23 +10007,48 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131025477</v>
+        <v>131024473</v>
       </c>
       <c r="B87" t="n">
         <v>57884</v>
@@ -10044,24 +10077,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464374</v>
+        <v>464305</v>
       </c>
       <c r="R87" t="n">
-        <v>7042300</v>
+        <v>7042334</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10098,7 +10123,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10109,48 +10134,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131025475</v>
+        <v>131025477</v>
       </c>
       <c r="B88" t="n">
         <v>57884</v>
@@ -10193,10 +10193,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464393</v>
+        <v>464374</v>
       </c>
       <c r="R88" t="n">
-        <v>7042284</v>
+        <v>7042300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10285,10 +10285,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131025496</v>
+        <v>131024475</v>
       </c>
       <c r="B89" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10296,34 +10296,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464485</v>
+        <v>464272</v>
       </c>
       <c r="R89" t="n">
-        <v>7042454</v>
+        <v>7042273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10375,22 +10375,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131025515</v>
+        <v>131024455</v>
       </c>
       <c r="B90" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10398,34 +10398,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464430</v>
+        <v>464454</v>
       </c>
       <c r="R90" t="n">
-        <v>7042344</v>
+        <v>7042523</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10477,19 +10477,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131024475</v>
+        <v>131024466</v>
       </c>
       <c r="B91" t="n">
         <v>57884</v>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464272</v>
+        <v>464319</v>
       </c>
       <c r="R91" t="n">
-        <v>7042273</v>
+        <v>7042385</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10591,10 +10591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131024455</v>
+        <v>131025496</v>
       </c>
       <c r="B92" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10602,34 +10602,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464454</v>
+        <v>464485</v>
       </c>
       <c r="R92" t="n">
-        <v>7042523</v>
+        <v>7042454</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10681,22 +10681,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131024466</v>
+        <v>131025515</v>
       </c>
       <c r="B93" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10704,34 +10704,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464319</v>
+        <v>464430</v>
       </c>
       <c r="R93" t="n">
-        <v>7042385</v>
+        <v>7042344</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10783,12 +10783,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10798,7 +10798,7 @@
         <v>131024512</v>
       </c>
       <c r="B94" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11028,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131024452</v>
+        <v>131025507</v>
       </c>
       <c r="B96" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11039,34 +11039,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464339</v>
+        <v>464297</v>
       </c>
       <c r="R96" t="n">
-        <v>7042474</v>
+        <v>7042525</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11118,19 +11118,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131025484</v>
+        <v>131024452</v>
       </c>
       <c r="B97" t="n">
         <v>57884</v>
@@ -11159,24 +11159,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464099</v>
+        <v>464339</v>
       </c>
       <c r="R97" t="n">
-        <v>7042646</v>
+        <v>7042474</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11213,7 +11205,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11224,51 +11216,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131025507</v>
+        <v>131025484</v>
       </c>
       <c r="B98" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11276,34 +11243,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464297</v>
+        <v>464099</v>
       </c>
       <c r="R98" t="n">
-        <v>7042525</v>
+        <v>7042646</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11340,7 +11315,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Ringhack, äldre, tydliga på gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,6 +11326,31 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024458</v>
+        <v>131024464</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464405</v>
+        <v>464337</v>
       </c>
       <c r="R21" t="n">
-        <v>7042391</v>
+        <v>7042380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024464</v>
+        <v>131025468</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -2839,16 +2839,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464337</v>
+        <v>464445</v>
       </c>
       <c r="R22" t="n">
-        <v>7042380</v>
+        <v>7042578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2893,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,23 +2904,48 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131025468</v>
+        <v>131024458</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2941,24 +2974,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464445</v>
+        <v>464405</v>
       </c>
       <c r="R23" t="n">
-        <v>7042578</v>
+        <v>7042391</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,51 +3031,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131024476</v>
+        <v>131025528</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464255</v>
+        <v>464199</v>
       </c>
       <c r="R24" t="n">
-        <v>7042273</v>
+        <v>7042793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131025474</v>
+        <v>131024476</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3178,24 +3178,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464391</v>
+        <v>464255</v>
       </c>
       <c r="R25" t="n">
-        <v>7042299</v>
+        <v>7042273</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3224,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,48 +3235,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131025470</v>
+        <v>131025474</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3327,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464484</v>
+        <v>464391</v>
       </c>
       <c r="R26" t="n">
-        <v>7042508</v>
+        <v>7042299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3334,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,7 +3386,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131024449</v>
+        <v>131025470</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3448,16 +3415,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464183</v>
+        <v>464484</v>
       </c>
       <c r="R27" t="n">
-        <v>7042531</v>
+        <v>7042508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3494,7 +3469,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,23 +3480,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024474</v>
+        <v>131024449</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464280</v>
+        <v>464183</v>
       </c>
       <c r="R28" t="n">
-        <v>7042322</v>
+        <v>7042531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131025485</v>
+        <v>131024474</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3652,24 +3652,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464186</v>
+        <v>464280</v>
       </c>
       <c r="R29" t="n">
-        <v>7042779</v>
+        <v>7042322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3698,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3717,51 +3709,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025528</v>
+        <v>131025485</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,34 +3736,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464199</v>
+        <v>464186</v>
       </c>
       <c r="R30" t="n">
-        <v>7042793</v>
+        <v>7042779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3808,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3844,6 +3819,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3860,7 +3860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025522</v>
+        <v>131025509</v>
       </c>
       <c r="B31" t="n">
         <v>79245</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463978</v>
+        <v>464380</v>
       </c>
       <c r="R31" t="n">
-        <v>7042528</v>
+        <v>7042615</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,7 +3962,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131025509</v>
+        <v>131025522</v>
       </c>
       <c r="B32" t="n">
         <v>79245</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464380</v>
+        <v>463978</v>
       </c>
       <c r="R32" t="n">
-        <v>7042615</v>
+        <v>7042528</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5865,10 +5865,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131024506</v>
+        <v>131025478</v>
       </c>
       <c r="B49" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5876,30 +5876,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464426</v>
+        <v>464380</v>
       </c>
       <c r="R49" t="n">
-        <v>7042565</v>
+        <v>7042301</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5934,6 +5946,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5942,26 +5959,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025511</v>
+        <v>131025471</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5969,34 +6011,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464483</v>
+        <v>464444</v>
       </c>
       <c r="R50" t="n">
-        <v>7042518</v>
+        <v>7042363</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6033,7 +6083,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6044,6 +6094,36 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6060,10 +6140,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025478</v>
+        <v>131025511</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6071,42 +6151,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464380</v>
+        <v>464483</v>
       </c>
       <c r="R51" t="n">
-        <v>7042301</v>
+        <v>7042518</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6143,7 +6215,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6154,31 +6226,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6195,7 +6242,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025471</v>
+        <v>131025482</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -6238,10 +6285,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464444</v>
+        <v>464034</v>
       </c>
       <c r="R52" t="n">
-        <v>7042363</v>
+        <v>7042322</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,7 +6325,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6293,11 +6340,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6335,10 +6377,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025482</v>
+        <v>131024506</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6346,42 +6388,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464034</v>
+        <v>464426</v>
       </c>
       <c r="R53" t="n">
-        <v>7042322</v>
+        <v>7042565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6416,11 +6446,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6429,41 +6454,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024463</v>
+        <v>131024511</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6680,23 +6680,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6704,10 +6700,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464371</v>
+        <v>463866</v>
       </c>
       <c r="R56" t="n">
-        <v>7042397</v>
+        <v>7042468</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6740,11 +6736,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6771,10 +6762,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131025483</v>
+        <v>131024510</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,42 +6773,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464021</v>
+        <v>464031</v>
       </c>
       <c r="R57" t="n">
-        <v>7042325</v>
+        <v>7042403</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6852,11 +6831,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6865,51 +6839,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131025469</v>
+        <v>131024507</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,42 +6866,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464464</v>
+        <v>464395</v>
       </c>
       <c r="R58" t="n">
-        <v>7042544</v>
+        <v>7042406</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6987,11 +6924,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7000,51 +6932,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024511</v>
+        <v>131024463</v>
       </c>
       <c r="B59" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,19 +6959,23 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7072,10 +6983,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463866</v>
+        <v>464371</v>
       </c>
       <c r="R59" t="n">
-        <v>7042468</v>
+        <v>7042397</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7108,6 +7019,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7134,10 +7050,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131024510</v>
+        <v>131025483</v>
       </c>
       <c r="B60" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7145,30 +7061,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464031</v>
+        <v>464021</v>
       </c>
       <c r="R60" t="n">
-        <v>7042403</v>
+        <v>7042325</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7203,6 +7131,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7211,26 +7144,51 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131024507</v>
+        <v>131025469</v>
       </c>
       <c r="B61" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7238,30 +7196,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464395</v>
+        <v>464464</v>
       </c>
       <c r="R61" t="n">
-        <v>7042406</v>
+        <v>7042544</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7296,6 +7266,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7304,16 +7279,41 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131024454</v>
+        <v>131025505</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464321</v>
+        <v>464214</v>
       </c>
       <c r="R2" t="n">
-        <v>7042482</v>
+        <v>7042578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131025505</v>
+        <v>131025514</v>
       </c>
       <c r="B3" t="n">
         <v>79245</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464214</v>
+        <v>464434</v>
       </c>
       <c r="R3" t="n">
-        <v>7042578</v>
+        <v>7042377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På flera granar vid en lucka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131025514</v>
+        <v>131024454</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464434</v>
+        <v>464321</v>
       </c>
       <c r="R4" t="n">
-        <v>7042377</v>
+        <v>7042482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På flera granar vid en lucka.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,12 +969,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -5865,10 +5865,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025478</v>
+        <v>131024506</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5876,42 +5876,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464380</v>
+        <v>464426</v>
       </c>
       <c r="R49" t="n">
-        <v>7042301</v>
+        <v>7042565</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5946,11 +5934,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5959,51 +5942,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025471</v>
+        <v>131025511</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6011,42 +5969,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464444</v>
+        <v>464483</v>
       </c>
       <c r="R50" t="n">
-        <v>7042363</v>
+        <v>7042518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6083,7 +6033,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6094,36 +6044,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6140,10 +6060,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025511</v>
+        <v>131025478</v>
       </c>
       <c r="B51" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6151,34 +6071,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464483</v>
+        <v>464380</v>
       </c>
       <c r="R51" t="n">
-        <v>7042518</v>
+        <v>7042301</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6215,7 +6143,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6226,6 +6154,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6242,7 +6195,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025482</v>
+        <v>131025471</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -6285,10 +6238,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464034</v>
+        <v>464444</v>
       </c>
       <c r="R52" t="n">
-        <v>7042322</v>
+        <v>7042363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6325,7 +6278,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6340,6 +6293,11 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -6377,10 +6335,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131024506</v>
+        <v>131025482</v>
       </c>
       <c r="B53" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6388,30 +6346,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464426</v>
+        <v>464034</v>
       </c>
       <c r="R53" t="n">
-        <v>7042565</v>
+        <v>7042322</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6446,6 +6416,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6454,16 +6429,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6669,10 +6669,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024511</v>
+        <v>131024463</v>
       </c>
       <c r="B56" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6680,19 +6680,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6700,10 +6704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>463866</v>
+        <v>464371</v>
       </c>
       <c r="R56" t="n">
-        <v>7042468</v>
+        <v>7042397</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6736,6 +6740,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6762,10 +6771,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024510</v>
+        <v>131025483</v>
       </c>
       <c r="B57" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6773,30 +6782,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464031</v>
+        <v>464021</v>
       </c>
       <c r="R57" t="n">
-        <v>7042403</v>
+        <v>7042325</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6831,6 +6852,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6839,26 +6865,51 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131024507</v>
+        <v>131025469</v>
       </c>
       <c r="B58" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6866,30 +6917,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464395</v>
+        <v>464464</v>
       </c>
       <c r="R58" t="n">
-        <v>7042406</v>
+        <v>7042544</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6924,6 +6987,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6932,26 +7000,51 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024463</v>
+        <v>131024511</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,23 +7052,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -6983,10 +7072,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464371</v>
+        <v>463866</v>
       </c>
       <c r="R59" t="n">
-        <v>7042397</v>
+        <v>7042468</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7019,11 +7108,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7050,10 +7134,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131025483</v>
+        <v>131024510</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7061,42 +7145,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464021</v>
+        <v>464031</v>
       </c>
       <c r="R60" t="n">
-        <v>7042325</v>
+        <v>7042403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7131,11 +7203,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7144,51 +7211,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131025469</v>
+        <v>131024507</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7196,42 +7238,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464464</v>
+        <v>464395</v>
       </c>
       <c r="R61" t="n">
-        <v>7042544</v>
+        <v>7042406</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7266,11 +7296,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7279,41 +7304,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -9625,10 +9625,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131025520</v>
+        <v>131024505</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>91830</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9636,34 +9636,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464027</v>
+        <v>464276</v>
       </c>
       <c r="R83" t="n">
-        <v>7042318</v>
+        <v>7042457</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9698,11 +9694,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9715,19 +9706,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131024505</v>
+        <v>131024508</v>
       </c>
       <c r="B84" t="n">
         <v>91830</v>
@@ -9758,10 +9749,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464276</v>
+        <v>464083</v>
       </c>
       <c r="R84" t="n">
-        <v>7042457</v>
+        <v>7042298</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9820,10 +9811,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131024508</v>
+        <v>131025520</v>
       </c>
       <c r="B85" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9831,30 +9822,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464083</v>
+        <v>464027</v>
       </c>
       <c r="R85" t="n">
-        <v>7042298</v>
+        <v>7042318</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9889,6 +9884,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9901,12 +9901,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131025526</v>
+        <v>131025513</v>
       </c>
       <c r="B5" t="n">
         <v>79245</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464101</v>
+        <v>464484</v>
       </c>
       <c r="R5" t="n">
-        <v>7042665</v>
+        <v>7042425</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025513</v>
+        <v>131025526</v>
       </c>
       <c r="B6" t="n">
         <v>79245</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464484</v>
+        <v>464101</v>
       </c>
       <c r="R6" t="n">
-        <v>7042425</v>
+        <v>7042665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025494</v>
+        <v>131025519</v>
       </c>
       <c r="B9" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,19 +1433,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1453,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464471</v>
+        <v>464076</v>
       </c>
       <c r="R9" t="n">
-        <v>7042462</v>
+        <v>7042281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025519</v>
+        <v>131025518</v>
       </c>
       <c r="B10" t="n">
         <v>79245</v>
@@ -1555,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464076</v>
+        <v>464161</v>
       </c>
       <c r="R10" t="n">
-        <v>7042281</v>
+        <v>7042247</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1599,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025502</v>
+        <v>131024467</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1633,34 +1637,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464177</v>
+        <v>464322</v>
       </c>
       <c r="R11" t="n">
-        <v>7042606</v>
+        <v>7042355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1712,22 +1716,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025506</v>
+        <v>131025463</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,34 +1739,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464253</v>
+        <v>464211</v>
       </c>
       <c r="R12" t="n">
-        <v>7042536</v>
+        <v>7042581</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1811,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,6 +1822,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1826,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025512</v>
+        <v>131025494</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1837,23 +1874,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1861,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464451</v>
+        <v>464471</v>
       </c>
       <c r="R13" t="n">
-        <v>7042487</v>
+        <v>7042462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,7 +1934,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,7 +1961,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025518</v>
+        <v>131025506</v>
       </c>
       <c r="B14" t="n">
         <v>79245</v>
@@ -1963,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464161</v>
+        <v>464253</v>
       </c>
       <c r="R14" t="n">
-        <v>7042247</v>
+        <v>7042536</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2003,7 +2036,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025488</v>
+        <v>131025502</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,42 +2074,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463958</v>
+        <v>464177</v>
       </c>
       <c r="R15" t="n">
-        <v>7042484</v>
+        <v>7042606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2138,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,31 +2149,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2165,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131024467</v>
+        <v>131025512</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,34 +2176,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464322</v>
+        <v>464451</v>
       </c>
       <c r="R16" t="n">
-        <v>7042355</v>
+        <v>7042487</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,22 +2255,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131025463</v>
+        <v>131025488</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464211</v>
+        <v>463958</v>
       </c>
       <c r="R17" t="n">
-        <v>7042581</v>
+        <v>7042484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2402,7 +2402,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131025525</v>
+        <v>131025510</v>
       </c>
       <c r="B18" t="n">
         <v>79245</v>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464067</v>
+        <v>464463</v>
       </c>
       <c r="R18" t="n">
-        <v>7042585</v>
+        <v>7042542</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,7 +2504,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131025510</v>
+        <v>131025525</v>
       </c>
       <c r="B19" t="n">
         <v>79245</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464463</v>
+        <v>464067</v>
       </c>
       <c r="R19" t="n">
-        <v>7042542</v>
+        <v>7042585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024464</v>
+        <v>131024458</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464337</v>
+        <v>464405</v>
       </c>
       <c r="R21" t="n">
-        <v>7042380</v>
+        <v>7042391</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131025468</v>
+        <v>131024464</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -2839,24 +2839,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464445</v>
+        <v>464337</v>
       </c>
       <c r="R22" t="n">
-        <v>7042578</v>
+        <v>7042380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2904,48 +2896,23 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131024458</v>
+        <v>131025468</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2974,16 +2941,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464405</v>
+        <v>464445</v>
       </c>
       <c r="R23" t="n">
-        <v>7042391</v>
+        <v>7042578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +2995,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,26 +3006,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131025528</v>
+        <v>131024476</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464199</v>
+        <v>464255</v>
       </c>
       <c r="R24" t="n">
-        <v>7042793</v>
+        <v>7042273</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131024476</v>
+        <v>131025474</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3178,16 +3178,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464255</v>
+        <v>464391</v>
       </c>
       <c r="R25" t="n">
-        <v>7042273</v>
+        <v>7042299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,7 +3232,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,23 +3243,48 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131025474</v>
+        <v>131025470</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3294,10 +3327,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464391</v>
+        <v>464484</v>
       </c>
       <c r="R26" t="n">
-        <v>7042299</v>
+        <v>7042508</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3367,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,7 +3419,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131025470</v>
+        <v>131024449</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3415,24 +3448,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464484</v>
+        <v>464183</v>
       </c>
       <c r="R27" t="n">
-        <v>7042508</v>
+        <v>7042531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3494,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3480,48 +3505,23 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024449</v>
+        <v>131024474</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464183</v>
+        <v>464280</v>
       </c>
       <c r="R28" t="n">
-        <v>7042531</v>
+        <v>7042322</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131024474</v>
+        <v>131025485</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3652,16 +3652,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464280</v>
+        <v>464186</v>
       </c>
       <c r="R29" t="n">
-        <v>7042322</v>
+        <v>7042779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3706,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3709,26 +3717,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025485</v>
+        <v>131025528</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3736,42 +3769,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464186</v>
+        <v>464199</v>
       </c>
       <c r="R30" t="n">
-        <v>7042779</v>
+        <v>7042793</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3833,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3819,31 +3844,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3860,7 +3860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025509</v>
+        <v>131025522</v>
       </c>
       <c r="B31" t="n">
         <v>79245</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464380</v>
+        <v>463978</v>
       </c>
       <c r="R31" t="n">
-        <v>7042615</v>
+        <v>7042528</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,7 +3962,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131025522</v>
+        <v>131025509</v>
       </c>
       <c r="B32" t="n">
         <v>79245</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463978</v>
+        <v>464380</v>
       </c>
       <c r="R32" t="n">
-        <v>7042528</v>
+        <v>7042615</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4411,10 +4411,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131025465</v>
+        <v>131025489</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,29 +4422,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4454,10 +4453,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464268</v>
+        <v>464035</v>
       </c>
       <c r="R36" t="n">
-        <v>7042527</v>
+        <v>7042354</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4494,7 +4493,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,32 +4502,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131024448</v>
+        <v>131025517</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,34 +4557,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464165</v>
+        <v>464199</v>
       </c>
       <c r="R37" t="n">
-        <v>7042546</v>
+        <v>7042210</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4636,22 +4636,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131024478</v>
+        <v>131025527</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4659,34 +4659,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464232</v>
+        <v>464174</v>
       </c>
       <c r="R38" t="n">
-        <v>7042762</v>
+        <v>7042780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4738,19 +4738,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131025472</v>
+        <v>131025465</v>
       </c>
       <c r="B39" t="n">
         <v>57884</v>
@@ -4783,7 +4783,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464419</v>
+        <v>464268</v>
       </c>
       <c r="R39" t="n">
-        <v>7042316</v>
+        <v>7042527</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -4885,10 +4885,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131025517</v>
+        <v>131024448</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4896,34 +4896,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464199</v>
+        <v>464165</v>
       </c>
       <c r="R40" t="n">
-        <v>7042210</v>
+        <v>7042546</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4975,22 +4975,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131025489</v>
+        <v>131024478</v>
       </c>
       <c r="B41" t="n">
-        <v>80351</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4998,41 +4998,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464035</v>
+        <v>464232</v>
       </c>
       <c r="R41" t="n">
-        <v>7042354</v>
+        <v>7042762</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5069,7 +5062,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5078,54 +5071,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025527</v>
+        <v>131025472</v>
       </c>
       <c r="B42" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,34 +5100,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464174</v>
+        <v>464419</v>
       </c>
       <c r="R42" t="n">
-        <v>7042780</v>
+        <v>7042316</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,7 +5172,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,6 +5183,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5665,10 +5665,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025495</v>
+        <v>131024506</v>
       </c>
       <c r="B47" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5692,14 +5692,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>463986</v>
+        <v>464426</v>
       </c>
       <c r="R47" t="n">
-        <v>7042522</v>
+        <v>7042565</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5734,11 +5734,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>I stående död klen gran.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5751,22 +5746,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025524</v>
+        <v>131025495</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5774,23 +5769,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5798,10 +5789,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464041</v>
+        <v>463986</v>
       </c>
       <c r="R48" t="n">
-        <v>7042631</v>
+        <v>7042522</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5838,7 +5829,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5865,10 +5856,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131024506</v>
+        <v>131025524</v>
       </c>
       <c r="B49" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5876,30 +5867,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464426</v>
+        <v>464041</v>
       </c>
       <c r="R49" t="n">
-        <v>7042565</v>
+        <v>7042631</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5934,6 +5929,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gamgran.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5946,12 +5946,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6470,10 +6470,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131024501</v>
+        <v>131024511</v>
       </c>
       <c r="B54" t="n">
-        <v>91806</v>
+        <v>91833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,23 +6481,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6505,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464070</v>
+        <v>463866</v>
       </c>
       <c r="R54" t="n">
-        <v>7042517</v>
+        <v>7042468</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,10 +6563,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131025504</v>
+        <v>131024501</v>
       </c>
       <c r="B55" t="n">
-        <v>79245</v>
+        <v>91809</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6578,34 +6574,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464204</v>
+        <v>464070</v>
       </c>
       <c r="R55" t="n">
-        <v>7042559</v>
+        <v>7042517</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6640,11 +6636,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På gran.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6657,22 +6648,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024463</v>
+        <v>131024510</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6680,23 +6671,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6704,10 +6691,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464371</v>
+        <v>464031</v>
       </c>
       <c r="R56" t="n">
-        <v>7042397</v>
+        <v>7042403</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6740,11 +6727,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6771,10 +6753,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131025483</v>
+        <v>131024507</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6782,42 +6764,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464021</v>
+        <v>464395</v>
       </c>
       <c r="R57" t="n">
-        <v>7042325</v>
+        <v>7042406</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6852,11 +6822,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6865,51 +6830,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131025469</v>
+        <v>131025504</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,42 +6857,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464464</v>
+        <v>464204</v>
       </c>
       <c r="R58" t="n">
-        <v>7042544</v>
+        <v>7042559</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6989,7 +6921,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7000,31 +6932,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7041,10 +6948,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024511</v>
+        <v>131024463</v>
       </c>
       <c r="B59" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7052,19 +6959,23 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7072,10 +6983,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>463866</v>
+        <v>464371</v>
       </c>
       <c r="R59" t="n">
-        <v>7042468</v>
+        <v>7042397</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7108,6 +7019,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7134,10 +7050,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131024510</v>
+        <v>131025483</v>
       </c>
       <c r="B60" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7145,30 +7061,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464031</v>
+        <v>464021</v>
       </c>
       <c r="R60" t="n">
-        <v>7042403</v>
+        <v>7042325</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7203,6 +7131,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7211,26 +7144,51 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131024507</v>
+        <v>131025469</v>
       </c>
       <c r="B61" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7238,30 +7196,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464395</v>
+        <v>464464</v>
       </c>
       <c r="R61" t="n">
-        <v>7042406</v>
+        <v>7042544</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7296,6 +7266,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7304,16 +7279,41 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7626,10 +7626,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131024456</v>
+        <v>131024509</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>91833</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7637,23 +7637,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7661,10 +7657,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464439</v>
+        <v>464214</v>
       </c>
       <c r="R65" t="n">
-        <v>7042505</v>
+        <v>7042282</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7697,11 +7693,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7728,27 +7719,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131024494</v>
+        <v>131024456</v>
       </c>
       <c r="B66" t="n">
-        <v>57988</v>
+        <v>57884</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7756,29 +7747,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464304</v>
+        <v>464439</v>
       </c>
       <c r="R66" t="n">
-        <v>7042379</v>
+        <v>7042505</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7811,6 +7790,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7837,41 +7821,57 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131024509</v>
+        <v>131024494</v>
       </c>
       <c r="B67" t="n">
-        <v>91830</v>
+        <v>57988</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464214</v>
+        <v>464304</v>
       </c>
       <c r="R67" t="n">
-        <v>7042282</v>
+        <v>7042379</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131025521</v>
+        <v>131024453</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8517,34 +8517,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464007</v>
+        <v>464327</v>
       </c>
       <c r="R73" t="n">
-        <v>7042409</v>
+        <v>7042477</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,19 +8596,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131024453</v>
+        <v>131024451</v>
       </c>
       <c r="B74" t="n">
         <v>57884</v>
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464327</v>
+        <v>464275</v>
       </c>
       <c r="R74" t="n">
-        <v>7042477</v>
+        <v>7042455</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8710,7 +8710,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131024451</v>
+        <v>131025480</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8739,16 +8739,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464275</v>
+        <v>464378</v>
       </c>
       <c r="R75" t="n">
-        <v>7042455</v>
+        <v>7042302</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8785,7 +8793,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8796,26 +8804,51 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131025480</v>
+        <v>131025521</v>
       </c>
       <c r="B76" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8823,42 +8856,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464378</v>
+        <v>464007</v>
       </c>
       <c r="R76" t="n">
-        <v>7042302</v>
+        <v>7042409</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8895,7 +8920,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8906,31 +8931,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9286,10 +9286,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131024470</v>
+        <v>131025492</v>
       </c>
       <c r="B80" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9297,34 +9297,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464325</v>
+        <v>464400</v>
       </c>
       <c r="R80" t="n">
-        <v>7042334</v>
+        <v>7042294</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9361,7 +9368,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9370,25 +9377,51 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131024461</v>
+        <v>131024470</v>
       </c>
       <c r="B81" t="n">
         <v>57884</v>
@@ -9423,10 +9456,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464377</v>
+        <v>464325</v>
       </c>
       <c r="R81" t="n">
-        <v>7042402</v>
+        <v>7042334</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9463,7 +9496,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9490,10 +9523,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131025492</v>
+        <v>131024461</v>
       </c>
       <c r="B82" t="n">
-        <v>91806</v>
+        <v>57884</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9501,41 +9534,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464400</v>
+        <v>464377</v>
       </c>
       <c r="R82" t="n">
-        <v>7042294</v>
+        <v>7042402</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9572,7 +9598,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9581,44 +9607,18 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9628,7 +9628,7 @@
         <v>131024505</v>
       </c>
       <c r="B83" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>131024508</v>
       </c>
       <c r="B84" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131024475</v>
+        <v>131025515</v>
       </c>
       <c r="B89" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10296,34 +10296,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464272</v>
+        <v>464430</v>
       </c>
       <c r="R89" t="n">
-        <v>7042273</v>
+        <v>7042344</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10375,22 +10375,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131024455</v>
+        <v>131025496</v>
       </c>
       <c r="B90" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10398,34 +10398,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464454</v>
+        <v>464485</v>
       </c>
       <c r="R90" t="n">
-        <v>7042523</v>
+        <v>7042454</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10477,19 +10477,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131024466</v>
+        <v>131024475</v>
       </c>
       <c r="B91" t="n">
         <v>57884</v>
@@ -10524,10 +10524,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464319</v>
+        <v>464272</v>
       </c>
       <c r="R91" t="n">
-        <v>7042385</v>
+        <v>7042273</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10591,10 +10591,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131025496</v>
+        <v>131024455</v>
       </c>
       <c r="B92" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10602,34 +10602,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464485</v>
+        <v>464454</v>
       </c>
       <c r="R92" t="n">
-        <v>7042454</v>
+        <v>7042523</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10681,22 +10681,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131025515</v>
+        <v>131024466</v>
       </c>
       <c r="B93" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10704,34 +10704,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464430</v>
+        <v>464319</v>
       </c>
       <c r="R93" t="n">
-        <v>7042344</v>
+        <v>7042385</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10783,12 +10783,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10798,7 +10798,7 @@
         <v>131024512</v>
       </c>
       <c r="B94" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131025505</v>
       </c>
       <c r="B2" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131025514</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131025513</v>
+        <v>131025526</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464484</v>
+        <v>464101</v>
       </c>
       <c r="R5" t="n">
-        <v>7042425</v>
+        <v>7042665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025526</v>
+        <v>131025513</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464101</v>
+        <v>464484</v>
       </c>
       <c r="R6" t="n">
-        <v>7042665</v>
+        <v>7042425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025519</v>
+        <v>131025494</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,23 +1433,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1457,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464076</v>
+        <v>464471</v>
       </c>
       <c r="R9" t="n">
-        <v>7042281</v>
+        <v>7042462</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1493,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025518</v>
+        <v>131025488</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1535,34 +1531,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464161</v>
+        <v>463958</v>
       </c>
       <c r="R10" t="n">
-        <v>7042247</v>
+        <v>7042484</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,7 +1603,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,6 +1614,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1863,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025494</v>
+        <v>131025506</v>
       </c>
       <c r="B13" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,19 +1903,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1894,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464471</v>
+        <v>464253</v>
       </c>
       <c r="R13" t="n">
-        <v>7042462</v>
+        <v>7042536</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1967,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025506</v>
+        <v>131025502</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1996,10 +2029,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464253</v>
+        <v>464177</v>
       </c>
       <c r="R14" t="n">
-        <v>7042536</v>
+        <v>7042606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2069,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025502</v>
+        <v>131025519</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2131,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464177</v>
+        <v>464076</v>
       </c>
       <c r="R15" t="n">
-        <v>7042606</v>
+        <v>7042281</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2171,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2201,7 @@
         <v>131025512</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131025488</v>
+        <v>131025518</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2278,42 +2311,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463958</v>
+        <v>464161</v>
       </c>
       <c r="R17" t="n">
-        <v>7042484</v>
+        <v>7042247</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2375,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2361,31 +2386,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131025510</v>
+        <v>131025525</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464463</v>
+        <v>464067</v>
       </c>
       <c r="R18" t="n">
-        <v>7042542</v>
+        <v>7042585</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131025525</v>
+        <v>131024468</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,34 +2515,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464067</v>
+        <v>464332</v>
       </c>
       <c r="R19" t="n">
-        <v>7042585</v>
+        <v>7042344</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,19 +2594,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131024468</v>
+        <v>131024458</v>
       </c>
       <c r="B20" t="n">
         <v>57884</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464332</v>
+        <v>464405</v>
       </c>
       <c r="R20" t="n">
-        <v>7042344</v>
+        <v>7042391</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024458</v>
+        <v>131024464</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464405</v>
+        <v>464337</v>
       </c>
       <c r="R21" t="n">
-        <v>7042391</v>
+        <v>7042380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024464</v>
+        <v>131025468</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -2839,16 +2839,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464337</v>
+        <v>464445</v>
       </c>
       <c r="R22" t="n">
-        <v>7042380</v>
+        <v>7042578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2893,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,26 +2904,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131025468</v>
+        <v>131025510</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,42 +2956,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464445</v>
+        <v>464463</v>
       </c>
       <c r="R23" t="n">
-        <v>7042578</v>
+        <v>7042542</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +3020,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,31 +3031,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3047,10 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131024476</v>
+        <v>131025528</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3058,34 +3058,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464255</v>
+        <v>464199</v>
       </c>
       <c r="R24" t="n">
-        <v>7042273</v>
+        <v>7042793</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3137,19 +3137,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131025474</v>
+        <v>131024476</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3178,24 +3178,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464391</v>
+        <v>464255</v>
       </c>
       <c r="R25" t="n">
-        <v>7042299</v>
+        <v>7042273</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3224,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,48 +3235,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131025470</v>
+        <v>131025474</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3327,10 +3294,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464484</v>
+        <v>464391</v>
       </c>
       <c r="R26" t="n">
-        <v>7042508</v>
+        <v>7042299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3367,7 +3334,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3419,7 +3386,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131024449</v>
+        <v>131025470</v>
       </c>
       <c r="B27" t="n">
         <v>57884</v>
@@ -3448,16 +3415,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464183</v>
+        <v>464484</v>
       </c>
       <c r="R27" t="n">
-        <v>7042531</v>
+        <v>7042508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3494,7 +3469,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3505,23 +3480,48 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024474</v>
+        <v>131024449</v>
       </c>
       <c r="B28" t="n">
         <v>57884</v>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464280</v>
+        <v>464183</v>
       </c>
       <c r="R28" t="n">
-        <v>7042322</v>
+        <v>7042531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3623,7 +3623,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131025485</v>
+        <v>131024474</v>
       </c>
       <c r="B29" t="n">
         <v>57884</v>
@@ -3652,24 +3652,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464186</v>
+        <v>464280</v>
       </c>
       <c r="R29" t="n">
-        <v>7042779</v>
+        <v>7042322</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,7 +3698,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3717,51 +3709,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025528</v>
+        <v>131025485</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,34 +3736,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464199</v>
+        <v>464186</v>
       </c>
       <c r="R30" t="n">
-        <v>7042793</v>
+        <v>7042779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3833,7 +3808,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3844,6 +3819,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3863,7 +3863,7 @@
         <v>131025522</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>131025509</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>131025489</v>
       </c>
       <c r="B36" t="n">
-        <v>80351</v>
+        <v>80352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>131025517</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>131025527</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131024462</v>
+        <v>131024459</v>
       </c>
       <c r="B43" t="n">
         <v>57884</v>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464376</v>
+        <v>464397</v>
       </c>
       <c r="R43" t="n">
-        <v>7042402</v>
+        <v>7042399</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131024457</v>
+        <v>131024462</v>
       </c>
       <c r="B44" t="n">
         <v>57884</v>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464399</v>
+        <v>464376</v>
       </c>
       <c r="R44" t="n">
-        <v>7042460</v>
+        <v>7042402</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,7 +5428,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131025466</v>
+        <v>131024457</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5457,24 +5457,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464389</v>
+        <v>464399</v>
       </c>
       <c r="R45" t="n">
-        <v>7042585</v>
+        <v>7042460</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5511,7 +5503,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5522,48 +5514,23 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131024459</v>
+        <v>131025466</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5592,16 +5559,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464397</v>
+        <v>464389</v>
       </c>
       <c r="R46" t="n">
-        <v>7042399</v>
+        <v>7042585</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5638,7 +5613,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5649,26 +5624,51 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131024506</v>
+        <v>131025511</v>
       </c>
       <c r="B47" t="n">
-        <v>91833</v>
+        <v>79246</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,30 +5676,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464426</v>
+        <v>464483</v>
       </c>
       <c r="R47" t="n">
-        <v>7042565</v>
+        <v>7042518</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5734,6 +5738,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5746,22 +5755,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025495</v>
+        <v>131025478</v>
       </c>
       <c r="B48" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5769,30 +5778,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463986</v>
+        <v>464380</v>
       </c>
       <c r="R48" t="n">
-        <v>7042522</v>
+        <v>7042301</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5829,7 +5850,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5840,6 +5861,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5856,10 +5902,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025524</v>
+        <v>131025471</v>
       </c>
       <c r="B49" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5867,34 +5913,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464041</v>
+        <v>464444</v>
       </c>
       <c r="R49" t="n">
-        <v>7042631</v>
+        <v>7042363</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5931,7 +5985,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,6 +5996,36 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5958,10 +6042,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025511</v>
+        <v>131025482</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5969,34 +6053,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464483</v>
+        <v>464034</v>
       </c>
       <c r="R50" t="n">
-        <v>7042518</v>
+        <v>7042322</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6033,7 +6125,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6044,6 +6136,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6060,10 +6177,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025478</v>
+        <v>131024506</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6071,42 +6188,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464380</v>
+        <v>464426</v>
       </c>
       <c r="R51" t="n">
-        <v>7042301</v>
+        <v>7042565</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6141,11 +6246,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6154,51 +6254,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025471</v>
+        <v>131025495</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6206,42 +6281,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464444</v>
+        <v>463986</v>
       </c>
       <c r="R52" t="n">
-        <v>7042363</v>
+        <v>7042522</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,7 +6341,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6289,36 +6352,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6335,10 +6368,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025482</v>
+        <v>131025524</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6346,42 +6379,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464034</v>
+        <v>464041</v>
       </c>
       <c r="R53" t="n">
-        <v>7042322</v>
+        <v>7042631</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6443,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,31 +6454,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6470,10 +6470,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131024511</v>
+        <v>131024501</v>
       </c>
       <c r="B54" t="n">
-        <v>91833</v>
+        <v>91810</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,19 +6481,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6501,10 +6505,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463866</v>
+        <v>464070</v>
       </c>
       <c r="R54" t="n">
-        <v>7042468</v>
+        <v>7042517</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6563,10 +6567,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131024501</v>
+        <v>131024511</v>
       </c>
       <c r="B55" t="n">
-        <v>91809</v>
+        <v>91834</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6574,23 +6578,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6598,10 +6598,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464070</v>
+        <v>463866</v>
       </c>
       <c r="R55" t="n">
-        <v>7042517</v>
+        <v>7042468</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024510</v>
+        <v>131024507</v>
       </c>
       <c r="B56" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464031</v>
+        <v>464395</v>
       </c>
       <c r="R56" t="n">
-        <v>7042403</v>
+        <v>7042406</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024507</v>
+        <v>131024510</v>
       </c>
       <c r="B57" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464395</v>
+        <v>464031</v>
       </c>
       <c r="R57" t="n">
-        <v>7042406</v>
+        <v>7042403</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6849,7 +6849,7 @@
         <v>131025504</v>
       </c>
       <c r="B58" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>131025508</v>
       </c>
       <c r="B62" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>131024509</v>
       </c>
       <c r="B65" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>131025516</v>
       </c>
       <c r="B68" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131024451</v>
+        <v>131025521</v>
       </c>
       <c r="B74" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8619,34 +8619,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464275</v>
+        <v>464007</v>
       </c>
       <c r="R74" t="n">
-        <v>7042455</v>
+        <v>7042409</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8698,19 +8698,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131025480</v>
+        <v>131024451</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8739,24 +8739,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464378</v>
+        <v>464275</v>
       </c>
       <c r="R75" t="n">
-        <v>7042302</v>
+        <v>7042455</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8793,7 +8785,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8804,51 +8796,26 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131025521</v>
+        <v>131025480</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8856,34 +8823,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464007</v>
+        <v>464378</v>
       </c>
       <c r="R76" t="n">
-        <v>7042409</v>
+        <v>7042302</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8920,7 +8895,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8931,6 +8906,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8950,7 +8950,7 @@
         <v>131025490</v>
       </c>
       <c r="B77" t="n">
-        <v>80351</v>
+        <v>80352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131025523</v>
+        <v>131025492</v>
       </c>
       <c r="B78" t="n">
-        <v>79245</v>
+        <v>91810</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,34 +9093,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>463999</v>
+        <v>464400</v>
       </c>
       <c r="R78" t="n">
-        <v>7042559</v>
+        <v>7042294</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9157,7 +9164,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9166,8 +9173,34 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9187,7 +9220,7 @@
         <v>131025503</v>
       </c>
       <c r="B79" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9286,10 +9319,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131025492</v>
+        <v>131025523</v>
       </c>
       <c r="B80" t="n">
-        <v>91809</v>
+        <v>79246</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9297,41 +9330,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464400</v>
+        <v>463999</v>
       </c>
       <c r="R80" t="n">
-        <v>7042294</v>
+        <v>7042559</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9368,7 +9394,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9377,34 +9403,8 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9625,10 +9625,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131024505</v>
+        <v>131024508</v>
       </c>
       <c r="B83" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9656,10 +9656,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464276</v>
+        <v>464083</v>
       </c>
       <c r="R83" t="n">
-        <v>7042457</v>
+        <v>7042298</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9718,10 +9718,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131024508</v>
+        <v>131024505</v>
       </c>
       <c r="B84" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9749,10 +9749,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464083</v>
+        <v>464276</v>
       </c>
       <c r="R84" t="n">
-        <v>7042298</v>
+        <v>7042457</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9814,7 +9814,7 @@
         <v>131025520</v>
       </c>
       <c r="B85" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131025515</v>
+        <v>131025496</v>
       </c>
       <c r="B89" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464430</v>
+        <v>464485</v>
       </c>
       <c r="R89" t="n">
-        <v>7042344</v>
+        <v>7042454</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10387,10 +10387,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131025496</v>
+        <v>131025515</v>
       </c>
       <c r="B90" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464485</v>
+        <v>464430</v>
       </c>
       <c r="R90" t="n">
-        <v>7042454</v>
+        <v>7042344</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10798,7 +10798,7 @@
         <v>131024512</v>
       </c>
       <c r="B94" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11028,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131025507</v>
+        <v>131024452</v>
       </c>
       <c r="B96" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11039,34 +11039,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464297</v>
+        <v>464339</v>
       </c>
       <c r="R96" t="n">
-        <v>7042525</v>
+        <v>7042474</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11118,19 +11118,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131024452</v>
+        <v>131025484</v>
       </c>
       <c r="B97" t="n">
         <v>57884</v>
@@ -11159,16 +11159,24 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464339</v>
+        <v>464099</v>
       </c>
       <c r="R97" t="n">
-        <v>7042474</v>
+        <v>7042646</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11205,7 +11213,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11216,26 +11224,51 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131025484</v>
+        <v>131025507</v>
       </c>
       <c r="B98" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11243,42 +11276,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464099</v>
+        <v>464297</v>
       </c>
       <c r="R98" t="n">
-        <v>7042646</v>
+        <v>7042525</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11315,7 +11340,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på gran.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11326,31 +11351,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025488</v>
+        <v>131025506</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,42 +1531,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463958</v>
+        <v>464253</v>
       </c>
       <c r="R10" t="n">
-        <v>7042484</v>
+        <v>7042536</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1595,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,31 +1606,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1655,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131024467</v>
+        <v>131025502</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,34 +1633,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464322</v>
+        <v>464177</v>
       </c>
       <c r="R11" t="n">
-        <v>7042355</v>
+        <v>7042606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1697,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,22 +1712,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025463</v>
+        <v>131025519</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,42 +1735,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464211</v>
+        <v>464076</v>
       </c>
       <c r="R12" t="n">
-        <v>7042581</v>
+        <v>7042281</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1799,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,31 +1810,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1892,7 +1826,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025506</v>
+        <v>131025512</v>
       </c>
       <c r="B13" t="n">
         <v>79246</v>
@@ -1927,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464253</v>
+        <v>464451</v>
       </c>
       <c r="R13" t="n">
-        <v>7042536</v>
+        <v>7042487</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1901,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,7 +1928,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025502</v>
+        <v>131025518</v>
       </c>
       <c r="B14" t="n">
         <v>79246</v>
@@ -2029,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464177</v>
+        <v>464161</v>
       </c>
       <c r="R14" t="n">
-        <v>7042606</v>
+        <v>7042247</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2096,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025519</v>
+        <v>131025488</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2107,34 +2041,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464076</v>
+        <v>463958</v>
       </c>
       <c r="R15" t="n">
-        <v>7042281</v>
+        <v>7042484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2171,7 +2113,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,6 +2124,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2198,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131025512</v>
+        <v>131024467</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,34 +2176,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464451</v>
+        <v>464322</v>
       </c>
       <c r="R16" t="n">
-        <v>7042487</v>
+        <v>7042355</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,7 +2240,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,22 +2255,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131025518</v>
+        <v>131025463</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2311,34 +2278,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464161</v>
+        <v>464211</v>
       </c>
       <c r="R17" t="n">
-        <v>7042247</v>
+        <v>7042581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2375,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,6 +2361,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -4546,7 +4546,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131025517</v>
+        <v>131025527</v>
       </c>
       <c r="B37" t="n">
         <v>79246</v>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464199</v>
+        <v>464174</v>
       </c>
       <c r="R37" t="n">
-        <v>7042210</v>
+        <v>7042780</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,10 +4648,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025527</v>
+        <v>131025465</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4659,34 +4659,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464174</v>
+        <v>464268</v>
       </c>
       <c r="R38" t="n">
-        <v>7042780</v>
+        <v>7042527</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4723,7 +4731,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4734,6 +4742,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4750,7 +4783,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131025465</v>
+        <v>131024448</v>
       </c>
       <c r="B39" t="n">
         <v>57884</v>
@@ -4779,24 +4812,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464268</v>
+        <v>464165</v>
       </c>
       <c r="R39" t="n">
-        <v>7042527</v>
+        <v>7042546</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4858,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4844,48 +4869,23 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131024448</v>
+        <v>131024478</v>
       </c>
       <c r="B40" t="n">
         <v>57884</v>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464165</v>
+        <v>464232</v>
       </c>
       <c r="R40" t="n">
-        <v>7042546</v>
+        <v>7042762</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4987,7 +4987,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131024478</v>
+        <v>131025472</v>
       </c>
       <c r="B41" t="n">
         <v>57884</v>
@@ -5016,16 +5016,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464232</v>
+        <v>464419</v>
       </c>
       <c r="R41" t="n">
-        <v>7042762</v>
+        <v>7042316</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5062,7 +5070,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5073,26 +5081,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025472</v>
+        <v>131025517</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,42 +5133,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464419</v>
+        <v>464199</v>
       </c>
       <c r="R42" t="n">
-        <v>7042316</v>
+        <v>7042210</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5172,7 +5197,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5183,31 +5208,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5665,10 +5665,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025511</v>
+        <v>131024506</v>
       </c>
       <c r="B47" t="n">
-        <v>79246</v>
+        <v>91834</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,34 +5676,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464483</v>
+        <v>464426</v>
       </c>
       <c r="R47" t="n">
-        <v>7042518</v>
+        <v>7042565</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5738,11 +5734,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5755,22 +5746,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025478</v>
+        <v>131025495</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5778,42 +5769,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464380</v>
+        <v>463986</v>
       </c>
       <c r="R48" t="n">
-        <v>7042301</v>
+        <v>7042522</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5850,7 +5829,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5861,31 +5840,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5902,10 +5856,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025471</v>
+        <v>131025524</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5913,42 +5867,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464444</v>
+        <v>464041</v>
       </c>
       <c r="R49" t="n">
-        <v>7042363</v>
+        <v>7042631</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5985,7 +5931,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,36 +5942,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6042,10 +5958,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025482</v>
+        <v>131025511</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6053,42 +5969,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464034</v>
+        <v>464483</v>
       </c>
       <c r="R50" t="n">
-        <v>7042322</v>
+        <v>7042518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6125,7 +6033,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,31 +6044,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6177,10 +6060,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131024506</v>
+        <v>131025478</v>
       </c>
       <c r="B51" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6188,30 +6071,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464426</v>
+        <v>464380</v>
       </c>
       <c r="R51" t="n">
-        <v>7042565</v>
+        <v>7042301</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6246,6 +6141,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6254,26 +6154,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025495</v>
+        <v>131025471</v>
       </c>
       <c r="B52" t="n">
-        <v>91834</v>
+        <v>57884</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6281,30 +6206,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>463986</v>
+        <v>464444</v>
       </c>
       <c r="R52" t="n">
-        <v>7042522</v>
+        <v>7042363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6341,7 +6278,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6352,6 +6289,36 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6368,10 +6335,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025524</v>
+        <v>131025482</v>
       </c>
       <c r="B53" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6379,34 +6346,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464041</v>
+        <v>464034</v>
       </c>
       <c r="R53" t="n">
-        <v>7042631</v>
+        <v>7042322</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6443,7 +6418,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6454,6 +6429,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6470,10 +6470,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131024501</v>
+        <v>131024511</v>
       </c>
       <c r="B54" t="n">
-        <v>91810</v>
+        <v>91834</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,23 +6481,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6505,10 +6501,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464070</v>
+        <v>463866</v>
       </c>
       <c r="R54" t="n">
-        <v>7042517</v>
+        <v>7042468</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6567,7 +6563,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131024511</v>
+        <v>131024507</v>
       </c>
       <c r="B55" t="n">
         <v>91834</v>
@@ -6598,10 +6594,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>463866</v>
+        <v>464395</v>
       </c>
       <c r="R55" t="n">
-        <v>7042468</v>
+        <v>7042406</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6660,7 +6656,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024507</v>
+        <v>131024510</v>
       </c>
       <c r="B56" t="n">
         <v>91834</v>
@@ -6691,10 +6687,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464395</v>
+        <v>464031</v>
       </c>
       <c r="R56" t="n">
-        <v>7042406</v>
+        <v>7042403</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6753,10 +6749,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024510</v>
+        <v>131025504</v>
       </c>
       <c r="B57" t="n">
-        <v>91834</v>
+        <v>79246</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6764,30 +6760,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464031</v>
+        <v>464204</v>
       </c>
       <c r="R57" t="n">
-        <v>7042403</v>
+        <v>7042559</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6822,6 +6822,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6834,22 +6839,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131025504</v>
+        <v>131024463</v>
       </c>
       <c r="B58" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6857,34 +6862,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464204</v>
+        <v>464371</v>
       </c>
       <c r="R58" t="n">
-        <v>7042559</v>
+        <v>7042397</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6921,7 +6926,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6936,19 +6941,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024463</v>
+        <v>131025483</v>
       </c>
       <c r="B59" t="n">
         <v>57884</v>
@@ -6977,16 +6982,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464371</v>
+        <v>464021</v>
       </c>
       <c r="R59" t="n">
-        <v>7042397</v>
+        <v>7042325</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7023,7 +7036,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7034,23 +7047,48 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131025483</v>
+        <v>131025469</v>
       </c>
       <c r="B60" t="n">
         <v>57884</v>
@@ -7083,7 +7121,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7093,10 +7131,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464021</v>
+        <v>464464</v>
       </c>
       <c r="R60" t="n">
-        <v>7042325</v>
+        <v>7042544</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +7171,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7162,12 +7200,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7185,10 +7223,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131025469</v>
+        <v>131024501</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>91810</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7196,42 +7234,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464464</v>
+        <v>464070</v>
       </c>
       <c r="R61" t="n">
-        <v>7042544</v>
+        <v>7042517</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7266,11 +7296,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7279,41 +7304,16 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7930,10 +7930,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131025516</v>
+        <v>131025479</v>
       </c>
       <c r="B68" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7941,34 +7941,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464319</v>
+        <v>464380</v>
       </c>
       <c r="R68" t="n">
-        <v>7042262</v>
+        <v>7042291</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8005,7 +8013,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8016,6 +8024,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8032,10 +8065,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131025479</v>
+        <v>131025516</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,42 +8076,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464380</v>
+        <v>464319</v>
       </c>
       <c r="R69" t="n">
-        <v>7042291</v>
+        <v>7042262</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +8140,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8126,31 +8151,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8506,10 +8506,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131024453</v>
+        <v>131025521</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8517,34 +8517,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464327</v>
+        <v>464007</v>
       </c>
       <c r="R73" t="n">
-        <v>7042477</v>
+        <v>7042409</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8596,22 +8596,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131025521</v>
+        <v>131024453</v>
       </c>
       <c r="B74" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8619,34 +8619,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464007</v>
+        <v>464327</v>
       </c>
       <c r="R74" t="n">
-        <v>7042409</v>
+        <v>7042477</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8698,12 +8698,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131025490</v>
+        <v>131025492</v>
       </c>
       <c r="B77" t="n">
-        <v>80352</v>
+        <v>91810</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,28 +8958,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>463994</v>
+        <v>464400</v>
       </c>
       <c r="R77" t="n">
-        <v>7042378</v>
+        <v>7042294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9049,22 +9049,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131025492</v>
+        <v>131024470</v>
       </c>
       <c r="B78" t="n">
-        <v>91810</v>
+        <v>57884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,41 +9093,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464400</v>
+        <v>464325</v>
       </c>
       <c r="R78" t="n">
-        <v>7042294</v>
+        <v>7042334</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9164,7 +9157,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9173,54 +9166,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131025503</v>
+        <v>131024461</v>
       </c>
       <c r="B79" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9228,34 +9195,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464158</v>
+        <v>464377</v>
       </c>
       <c r="R79" t="n">
-        <v>7042548</v>
+        <v>7042402</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9292,7 +9259,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9307,22 +9274,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131025523</v>
+        <v>131025490</v>
       </c>
       <c r="B80" t="n">
-        <v>79246</v>
+        <v>80352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9330,34 +9297,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>463999</v>
+        <v>463994</v>
       </c>
       <c r="R80" t="n">
-        <v>7042559</v>
+        <v>7042378</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9394,7 +9368,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9403,8 +9377,34 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131024470</v>
+        <v>131025523</v>
       </c>
       <c r="B81" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9432,34 +9432,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464325</v>
+        <v>463999</v>
       </c>
       <c r="R81" t="n">
-        <v>7042334</v>
+        <v>7042559</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9511,22 +9511,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131024461</v>
+        <v>131025503</v>
       </c>
       <c r="B82" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9534,34 +9534,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464377</v>
+        <v>464158</v>
       </c>
       <c r="R82" t="n">
-        <v>7042402</v>
+        <v>7042548</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9613,12 +9613,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9811,10 +9811,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131025520</v>
+        <v>131025475</v>
       </c>
       <c r="B85" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9822,34 +9822,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464027</v>
+        <v>464393</v>
       </c>
       <c r="R85" t="n">
-        <v>7042318</v>
+        <v>7042284</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9886,7 +9894,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9897,6 +9905,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9913,7 +9946,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131025475</v>
+        <v>131024473</v>
       </c>
       <c r="B86" t="n">
         <v>57884</v>
@@ -9942,24 +9975,16 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464393</v>
+        <v>464305</v>
       </c>
       <c r="R86" t="n">
-        <v>7042284</v>
+        <v>7042334</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,7 +10021,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10007,48 +10032,23 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131024473</v>
+        <v>131025477</v>
       </c>
       <c r="B87" t="n">
         <v>57884</v>
@@ -10077,16 +10077,24 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464305</v>
+        <v>464374</v>
       </c>
       <c r="R87" t="n">
-        <v>7042334</v>
+        <v>7042300</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10123,7 +10131,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10134,26 +10142,51 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131025477</v>
+        <v>131025520</v>
       </c>
       <c r="B88" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10161,42 +10194,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464374</v>
+        <v>464027</v>
       </c>
       <c r="R88" t="n">
-        <v>7042300</v>
+        <v>7042318</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10233,7 +10258,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10244,31 +10269,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11028,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131024452</v>
+        <v>131025507</v>
       </c>
       <c r="B96" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11039,34 +11039,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464339</v>
+        <v>464297</v>
       </c>
       <c r="R96" t="n">
-        <v>7042474</v>
+        <v>7042525</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11118,19 +11118,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131025484</v>
+        <v>131024452</v>
       </c>
       <c r="B97" t="n">
         <v>57884</v>
@@ -11159,24 +11159,16 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464099</v>
+        <v>464339</v>
       </c>
       <c r="R97" t="n">
-        <v>7042646</v>
+        <v>7042474</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11213,7 +11205,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11224,51 +11216,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131025507</v>
+        <v>131025484</v>
       </c>
       <c r="B98" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11276,34 +11243,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464297</v>
+        <v>464099</v>
       </c>
       <c r="R98" t="n">
-        <v>7042525</v>
+        <v>7042646</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11340,7 +11315,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Ringhack, äldre, tydliga på gran.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11351,6 +11326,31 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131025505</v>
       </c>
       <c r="B2" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131025514</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131024454</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131025526</v>
+        <v>131025513</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464101</v>
+        <v>464484</v>
       </c>
       <c r="R5" t="n">
-        <v>7042665</v>
+        <v>7042425</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025513</v>
+        <v>131025526</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464484</v>
+        <v>464101</v>
       </c>
       <c r="R6" t="n">
-        <v>7042425</v>
+        <v>7042665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,7 +1188,7 @@
         <v>131024469</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131025467</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
         <v>131025494</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025506</v>
+        <v>131025488</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,34 +1531,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464253</v>
+        <v>463958</v>
       </c>
       <c r="R10" t="n">
-        <v>7042536</v>
+        <v>7042484</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1603,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,6 +1614,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1622,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025502</v>
+        <v>131025506</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464177</v>
+        <v>464253</v>
       </c>
       <c r="R11" t="n">
-        <v>7042606</v>
+        <v>7042536</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,7 +1730,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,10 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025519</v>
+        <v>131025502</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464076</v>
+        <v>464177</v>
       </c>
       <c r="R12" t="n">
-        <v>7042281</v>
+        <v>7042606</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1832,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025512</v>
+        <v>131025519</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464451</v>
+        <v>464076</v>
       </c>
       <c r="R13" t="n">
-        <v>7042487</v>
+        <v>7042281</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,7 +1934,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025518</v>
+        <v>131025512</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464161</v>
+        <v>464451</v>
       </c>
       <c r="R14" t="n">
-        <v>7042247</v>
+        <v>7042487</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025488</v>
+        <v>131025518</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,42 +2074,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463958</v>
+        <v>464161</v>
       </c>
       <c r="R15" t="n">
-        <v>7042484</v>
+        <v>7042247</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,7 +2138,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2124,31 +2149,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2168,7 +2168,7 @@
         <v>131024467</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>131025463</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131025525</v>
+        <v>131025510</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464067</v>
+        <v>464463</v>
       </c>
       <c r="R18" t="n">
-        <v>7042585</v>
+        <v>7042542</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131024468</v>
+        <v>131025525</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2515,34 +2515,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464332</v>
+        <v>464067</v>
       </c>
       <c r="R19" t="n">
-        <v>7042344</v>
+        <v>7042585</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,22 +2594,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131024458</v>
+        <v>131024468</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464405</v>
+        <v>464332</v>
       </c>
       <c r="R20" t="n">
-        <v>7042391</v>
+        <v>7042344</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024464</v>
+        <v>131024458</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464337</v>
+        <v>464405</v>
       </c>
       <c r="R21" t="n">
-        <v>7042380</v>
+        <v>7042391</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131025468</v>
+        <v>131024464</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,24 +2839,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464445</v>
+        <v>464337</v>
       </c>
       <c r="R22" t="n">
-        <v>7042578</v>
+        <v>7042380</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,7 +2885,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2904,51 +2896,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131025510</v>
+        <v>131025468</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2956,34 +2923,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464463</v>
+        <v>464445</v>
       </c>
       <c r="R23" t="n">
-        <v>7042542</v>
+        <v>7042578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3020,7 +2995,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3031,6 +3006,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3050,7 +3050,7 @@
         <v>131025528</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>131024476</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>131025474</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         <v>131025470</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>131024449</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>131024474</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>131025485</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025522</v>
+        <v>131025509</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>463978</v>
+        <v>464380</v>
       </c>
       <c r="R31" t="n">
-        <v>7042528</v>
+        <v>7042615</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131025509</v>
+        <v>131025522</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464380</v>
+        <v>463978</v>
       </c>
       <c r="R32" t="n">
-        <v>7042615</v>
+        <v>7042528</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,7 +4067,7 @@
         <v>131024465</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>131024446</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>131025464</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>131025489</v>
       </c>
       <c r="B36" t="n">
-        <v>80352</v>
+        <v>80354</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4546,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131025527</v>
+        <v>131025517</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464174</v>
+        <v>464199</v>
       </c>
       <c r="R37" t="n">
-        <v>7042780</v>
+        <v>7042210</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4648,10 +4648,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025465</v>
+        <v>131025527</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4659,42 +4659,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464268</v>
+        <v>464174</v>
       </c>
       <c r="R38" t="n">
-        <v>7042527</v>
+        <v>7042780</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4731,7 +4723,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4742,31 +4734,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4783,10 +4750,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131024448</v>
+        <v>131025465</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4812,16 +4779,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464165</v>
+        <v>464268</v>
       </c>
       <c r="R39" t="n">
-        <v>7042546</v>
+        <v>7042527</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4858,7 +4833,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4869,26 +4844,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131024478</v>
+        <v>131024448</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464232</v>
+        <v>464165</v>
       </c>
       <c r="R40" t="n">
-        <v>7042762</v>
+        <v>7042546</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4987,10 +4987,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131025472</v>
+        <v>131024478</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5016,24 +5016,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464419</v>
+        <v>464232</v>
       </c>
       <c r="R41" t="n">
-        <v>7042316</v>
+        <v>7042762</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5070,7 +5062,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,51 +5073,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025517</v>
+        <v>131025472</v>
       </c>
       <c r="B42" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5133,34 +5100,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464199</v>
+        <v>464419</v>
       </c>
       <c r="R42" t="n">
-        <v>7042210</v>
+        <v>7042316</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,7 +5172,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5208,6 +5183,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5224,10 +5224,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131024459</v>
+        <v>131024462</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,10 +5259,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464397</v>
+        <v>464376</v>
       </c>
       <c r="R43" t="n">
-        <v>7042399</v>
+        <v>7042402</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131024462</v>
+        <v>131024457</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464376</v>
+        <v>464399</v>
       </c>
       <c r="R44" t="n">
-        <v>7042402</v>
+        <v>7042460</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131024457</v>
+        <v>131025466</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5457,16 +5457,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464399</v>
+        <v>464389</v>
       </c>
       <c r="R45" t="n">
-        <v>7042460</v>
+        <v>7042585</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,7 +5511,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5514,26 +5522,51 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131025466</v>
+        <v>131024459</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5559,24 +5592,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464389</v>
+        <v>464397</v>
       </c>
       <c r="R46" t="n">
-        <v>7042585</v>
+        <v>7042399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5613,7 +5638,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5624,51 +5649,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131024506</v>
+        <v>131025478</v>
       </c>
       <c r="B47" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,30 +5676,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464426</v>
+        <v>464380</v>
       </c>
       <c r="R47" t="n">
-        <v>7042565</v>
+        <v>7042301</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5734,6 +5746,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5742,26 +5759,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025495</v>
+        <v>131025471</v>
       </c>
       <c r="B48" t="n">
-        <v>91834</v>
+        <v>57886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5769,30 +5811,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463986</v>
+        <v>464444</v>
       </c>
       <c r="R48" t="n">
-        <v>7042522</v>
+        <v>7042363</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5829,7 +5883,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5840,6 +5894,36 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5856,10 +5940,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025524</v>
+        <v>131025482</v>
       </c>
       <c r="B49" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5867,34 +5951,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464041</v>
+        <v>464034</v>
       </c>
       <c r="R49" t="n">
-        <v>7042631</v>
+        <v>7042322</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5931,7 +6023,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5942,6 +6034,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5958,10 +6075,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025511</v>
+        <v>131024506</v>
       </c>
       <c r="B50" t="n">
-        <v>79246</v>
+        <v>91836</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5969,34 +6086,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464483</v>
+        <v>464426</v>
       </c>
       <c r="R50" t="n">
-        <v>7042518</v>
+        <v>7042565</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6031,11 +6144,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6048,22 +6156,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025478</v>
+        <v>131025495</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6071,42 +6179,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464380</v>
+        <v>463986</v>
       </c>
       <c r="R51" t="n">
-        <v>7042301</v>
+        <v>7042522</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6143,7 +6239,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6154,31 +6250,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6195,10 +6266,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025471</v>
+        <v>131025524</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6206,42 +6277,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464444</v>
+        <v>464041</v>
       </c>
       <c r="R52" t="n">
-        <v>7042363</v>
+        <v>7042631</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,7 +6341,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6289,36 +6352,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6335,10 +6368,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025482</v>
+        <v>131025511</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6346,42 +6379,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464034</v>
+        <v>464483</v>
       </c>
       <c r="R53" t="n">
-        <v>7042322</v>
+        <v>7042518</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6443,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,31 +6454,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6473,7 +6473,7 @@
         <v>131024511</v>
       </c>
       <c r="B54" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131024507</v>
+        <v>131024510</v>
       </c>
       <c r="B55" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464395</v>
+        <v>464031</v>
       </c>
       <c r="R55" t="n">
-        <v>7042406</v>
+        <v>7042403</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024510</v>
+        <v>131024507</v>
       </c>
       <c r="B56" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464031</v>
+        <v>464395</v>
       </c>
       <c r="R56" t="n">
-        <v>7042403</v>
+        <v>7042406</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131025504</v>
+        <v>131024463</v>
       </c>
       <c r="B57" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,34 +6760,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464204</v>
+        <v>464371</v>
       </c>
       <c r="R57" t="n">
-        <v>7042559</v>
+        <v>7042397</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6839,22 +6839,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131024463</v>
+        <v>131025483</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6880,16 +6880,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464371</v>
+        <v>464021</v>
       </c>
       <c r="R58" t="n">
-        <v>7042397</v>
+        <v>7042325</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6926,7 +6934,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6937,26 +6945,51 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131025483</v>
+        <v>131025469</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6986,7 +7019,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -6996,10 +7029,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464021</v>
+        <v>464464</v>
       </c>
       <c r="R59" t="n">
-        <v>7042325</v>
+        <v>7042544</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7036,7 +7069,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7065,12 +7098,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7088,10 +7121,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131025469</v>
+        <v>131024501</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>91812</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7099,42 +7132,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464464</v>
+        <v>464070</v>
       </c>
       <c r="R60" t="n">
-        <v>7042544</v>
+        <v>7042517</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7169,11 +7194,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7182,51 +7202,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131024501</v>
+        <v>131025504</v>
       </c>
       <c r="B61" t="n">
-        <v>91810</v>
+        <v>79248</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7234,34 +7229,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464070</v>
+        <v>464204</v>
       </c>
       <c r="R61" t="n">
-        <v>7042517</v>
+        <v>7042559</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7296,6 +7291,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7308,12 +7308,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7323,7 +7323,7 @@
         <v>131025508</v>
       </c>
       <c r="B62" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>131024460</v>
       </c>
       <c r="B63" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>131024450</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7626,41 +7626,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131024509</v>
+        <v>131024494</v>
       </c>
       <c r="B65" t="n">
-        <v>91834</v>
+        <v>57990</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464214</v>
+        <v>464304</v>
       </c>
       <c r="R65" t="n">
-        <v>7042282</v>
+        <v>7042379</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7719,10 +7735,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131024456</v>
+        <v>131024509</v>
       </c>
       <c r="B66" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7730,23 +7746,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7754,10 +7766,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464439</v>
+        <v>464214</v>
       </c>
       <c r="R66" t="n">
-        <v>7042505</v>
+        <v>7042282</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7790,11 +7802,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7821,27 +7828,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131024494</v>
+        <v>131024456</v>
       </c>
       <c r="B67" t="n">
-        <v>57988</v>
+        <v>57886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7849,29 +7856,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464304</v>
+        <v>464439</v>
       </c>
       <c r="R67" t="n">
-        <v>7042379</v>
+        <v>7042505</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7904,6 +7899,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7930,10 +7930,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131025479</v>
+        <v>131025516</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7941,42 +7941,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464380</v>
+        <v>464319</v>
       </c>
       <c r="R68" t="n">
-        <v>7042291</v>
+        <v>7042262</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8013,7 +8005,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8024,31 +8016,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8065,10 +8032,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131025516</v>
+        <v>131025479</v>
       </c>
       <c r="B69" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8076,34 +8043,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464319</v>
+        <v>464380</v>
       </c>
       <c r="R69" t="n">
-        <v>7042262</v>
+        <v>7042291</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8140,7 +8115,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8151,6 +8126,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8170,7 +8170,7 @@
         <v>131024472</v>
       </c>
       <c r="B70" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>131024477</v>
       </c>
       <c r="B71" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>131025481</v>
       </c>
       <c r="B72" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>131025521</v>
       </c>
       <c r="B73" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>131024453</v>
       </c>
       <c r="B74" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>131024451</v>
       </c>
       <c r="B75" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>131025480</v>
       </c>
       <c r="B76" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131025492</v>
+        <v>131025490</v>
       </c>
       <c r="B77" t="n">
-        <v>91810</v>
+        <v>80354</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,28 +8958,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464400</v>
+        <v>463994</v>
       </c>
       <c r="R77" t="n">
-        <v>7042294</v>
+        <v>7042378</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9049,22 +9049,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131024470</v>
+        <v>131025492</v>
       </c>
       <c r="B78" t="n">
-        <v>57884</v>
+        <v>91812</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,34 +9093,41 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464325</v>
+        <v>464400</v>
       </c>
       <c r="R78" t="n">
-        <v>7042334</v>
+        <v>7042294</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9157,7 +9164,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9166,28 +9173,54 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131024461</v>
+        <v>131025523</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9195,34 +9228,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464377</v>
+        <v>463999</v>
       </c>
       <c r="R79" t="n">
-        <v>7042402</v>
+        <v>7042559</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9259,7 +9292,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9274,22 +9307,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131025490</v>
+        <v>131025503</v>
       </c>
       <c r="B80" t="n">
-        <v>80352</v>
+        <v>79248</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9297,41 +9330,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>463994</v>
+        <v>464158</v>
       </c>
       <c r="R80" t="n">
-        <v>7042378</v>
+        <v>7042548</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9368,7 +9394,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9377,34 +9403,8 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131025523</v>
+        <v>131024470</v>
       </c>
       <c r="B81" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9432,34 +9432,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>463999</v>
+        <v>464325</v>
       </c>
       <c r="R81" t="n">
-        <v>7042559</v>
+        <v>7042334</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9511,22 +9511,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131025503</v>
+        <v>131024461</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9534,34 +9534,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464158</v>
+        <v>464377</v>
       </c>
       <c r="R82" t="n">
-        <v>7042548</v>
+        <v>7042402</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9613,22 +9613,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131024508</v>
+        <v>131025520</v>
       </c>
       <c r="B83" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9636,30 +9636,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464083</v>
+        <v>464027</v>
       </c>
       <c r="R83" t="n">
-        <v>7042298</v>
+        <v>7042318</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9694,6 +9698,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9706,12 +9715,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9721,7 +9730,7 @@
         <v>131024505</v>
       </c>
       <c r="B84" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9811,10 +9820,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131025475</v>
+        <v>131024508</v>
       </c>
       <c r="B85" t="n">
-        <v>57884</v>
+        <v>91836</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9822,42 +9831,30 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464393</v>
+        <v>464083</v>
       </c>
       <c r="R85" t="n">
-        <v>7042284</v>
+        <v>7042298</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9892,11 +9889,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9905,51 +9897,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131024473</v>
+        <v>131025475</v>
       </c>
       <c r="B86" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9975,16 +9942,24 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464305</v>
+        <v>464393</v>
       </c>
       <c r="R86" t="n">
-        <v>7042334</v>
+        <v>7042284</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10021,7 +9996,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10032,26 +10007,51 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131025477</v>
+        <v>131024473</v>
       </c>
       <c r="B87" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10077,24 +10077,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464374</v>
+        <v>464305</v>
       </c>
       <c r="R87" t="n">
-        <v>7042300</v>
+        <v>7042334</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10131,7 +10123,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10142,51 +10134,26 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131025520</v>
+        <v>131025477</v>
       </c>
       <c r="B88" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10194,34 +10161,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464027</v>
+        <v>464374</v>
       </c>
       <c r="R88" t="n">
-        <v>7042318</v>
+        <v>7042300</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10258,7 +10233,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10269,6 +10244,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10288,7 +10288,7 @@
         <v>131025496</v>
       </c>
       <c r="B89" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>131025515</v>
       </c>
       <c r="B90" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>131024475</v>
       </c>
       <c r="B91" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>131024455</v>
       </c>
       <c r="B92" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>131024466</v>
       </c>
       <c r="B93" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>131024512</v>
       </c>
       <c r="B94" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>131025473</v>
       </c>
       <c r="B95" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11028,10 +11028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131025507</v>
+        <v>131024452</v>
       </c>
       <c r="B96" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11039,34 +11039,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>464297</v>
+        <v>464339</v>
       </c>
       <c r="R96" t="n">
-        <v>7042525</v>
+        <v>7042474</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11118,22 +11118,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131024452</v>
+        <v>131025484</v>
       </c>
       <c r="B97" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11159,16 +11159,24 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>464339</v>
+        <v>464099</v>
       </c>
       <c r="R97" t="n">
-        <v>7042474</v>
+        <v>7042646</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11205,7 +11213,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på gran.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11216,26 +11224,51 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131025484</v>
+        <v>131025507</v>
       </c>
       <c r="B98" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11243,42 +11276,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>464099</v>
+        <v>464297</v>
       </c>
       <c r="R98" t="n">
-        <v>7042646</v>
+        <v>7042525</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11315,7 +11340,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, tydliga på gran.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11326,31 +11351,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131025505</v>
       </c>
       <c r="B2" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>131025514</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131024454</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131025513</v>
       </c>
       <c r="B5" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>131025526</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131024469</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131025467</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025494</v>
+        <v>131025506</v>
       </c>
       <c r="B9" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,19 +1433,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1453,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464471</v>
+        <v>464253</v>
       </c>
       <c r="R9" t="n">
-        <v>7042462</v>
+        <v>7042536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1497,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025488</v>
+        <v>131025502</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1531,42 +1535,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463958</v>
+        <v>464177</v>
       </c>
       <c r="R10" t="n">
-        <v>7042484</v>
+        <v>7042606</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1599,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,31 +1610,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1655,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025506</v>
+        <v>131025519</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,10 +1661,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464253</v>
+        <v>464076</v>
       </c>
       <c r="R11" t="n">
-        <v>7042536</v>
+        <v>7042281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1701,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025502</v>
+        <v>131025512</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464177</v>
+        <v>464451</v>
       </c>
       <c r="R12" t="n">
-        <v>7042606</v>
+        <v>7042487</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025519</v>
+        <v>131025518</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464076</v>
+        <v>464161</v>
       </c>
       <c r="R13" t="n">
-        <v>7042281</v>
+        <v>7042247</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1905,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1961,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025512</v>
+        <v>131025488</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,34 +1943,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464451</v>
+        <v>463958</v>
       </c>
       <c r="R14" t="n">
-        <v>7042487</v>
+        <v>7042484</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2015,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,6 +2026,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2063,10 +2067,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025518</v>
+        <v>131025494</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2074,23 +2078,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464161</v>
+        <v>464471</v>
       </c>
       <c r="R15" t="n">
-        <v>7042247</v>
+        <v>7042462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I granstubbe.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,7 +2168,7 @@
         <v>131024467</v>
       </c>
       <c r="B16" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>131025463</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131025510</v>
+        <v>131024458</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,34 +2413,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464463</v>
+        <v>464405</v>
       </c>
       <c r="R18" t="n">
-        <v>7042542</v>
+        <v>7042391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,12 +2492,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         <v>131025525</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131024468</v>
+        <v>131025510</v>
       </c>
       <c r="B20" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2617,34 +2617,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464332</v>
+        <v>464463</v>
       </c>
       <c r="R20" t="n">
-        <v>7042344</v>
+        <v>7042542</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2696,22 +2696,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024458</v>
+        <v>131024468</v>
       </c>
       <c r="B21" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464405</v>
+        <v>464332</v>
       </c>
       <c r="R21" t="n">
-        <v>7042391</v>
+        <v>7042344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2813,7 +2813,7 @@
         <v>131024464</v>
       </c>
       <c r="B22" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>131025468</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>131025528</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131024476</v>
+        <v>131024474</v>
       </c>
       <c r="B25" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,10 +3184,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464255</v>
+        <v>464280</v>
       </c>
       <c r="R25" t="n">
-        <v>7042273</v>
+        <v>7042322</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131025474</v>
+        <v>131024476</v>
       </c>
       <c r="B26" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3280,24 +3280,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464391</v>
+        <v>464255</v>
       </c>
       <c r="R26" t="n">
-        <v>7042299</v>
+        <v>7042273</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,7 +3326,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,51 +3337,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131025470</v>
+        <v>131025474</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3429,10 +3396,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464484</v>
+        <v>464391</v>
       </c>
       <c r="R27" t="n">
-        <v>7042508</v>
+        <v>7042299</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3469,7 +3436,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,10 +3488,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131024449</v>
+        <v>131025470</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3550,16 +3517,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464183</v>
+        <v>464484</v>
       </c>
       <c r="R28" t="n">
-        <v>7042531</v>
+        <v>7042508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3596,7 +3571,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3607,26 +3582,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131024474</v>
+        <v>131024449</v>
       </c>
       <c r="B29" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464280</v>
+        <v>464183</v>
       </c>
       <c r="R29" t="n">
-        <v>7042322</v>
+        <v>7042531</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,7 +3728,7 @@
         <v>131025485</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
         <v>131025509</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>131025522</v>
       </c>
       <c r="B32" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>131024465</v>
       </c>
       <c r="B33" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>131024446</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>131025464</v>
       </c>
       <c r="B35" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4411,10 +4411,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131025489</v>
+        <v>131025527</v>
       </c>
       <c r="B36" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,41 +4422,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464035</v>
+        <v>464174</v>
       </c>
       <c r="R36" t="n">
-        <v>7042354</v>
+        <v>7042780</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4493,7 +4486,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4502,34 +4495,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4549,7 +4516,7 @@
         <v>131025517</v>
       </c>
       <c r="B37" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4648,10 +4615,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025527</v>
+        <v>131025489</v>
       </c>
       <c r="B38" t="n">
-        <v>79248</v>
+        <v>80355</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4659,34 +4626,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464174</v>
+        <v>464035</v>
       </c>
       <c r="R38" t="n">
-        <v>7042780</v>
+        <v>7042354</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4723,7 +4697,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4732,8 +4706,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4753,7 +4753,7 @@
         <v>131025465</v>
       </c>
       <c r="B39" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4888,7 +4888,7 @@
         <v>131024448</v>
       </c>
       <c r="B40" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>131024478</v>
       </c>
       <c r="B41" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>131025472</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>131024462</v>
       </c>
       <c r="B43" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5326,10 +5326,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131024457</v>
+        <v>131025466</v>
       </c>
       <c r="B44" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,16 +5355,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464399</v>
+        <v>464389</v>
       </c>
       <c r="R44" t="n">
-        <v>7042460</v>
+        <v>7042585</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5401,7 +5409,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,26 +5420,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131025466</v>
+        <v>131024459</v>
       </c>
       <c r="B45" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5457,24 +5490,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464389</v>
+        <v>464397</v>
       </c>
       <c r="R45" t="n">
-        <v>7042585</v>
+        <v>7042399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5511,7 +5536,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5522,51 +5547,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131024459</v>
+        <v>131024457</v>
       </c>
       <c r="B46" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464397</v>
+        <v>464399</v>
       </c>
       <c r="R46" t="n">
-        <v>7042399</v>
+        <v>7042460</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5665,10 +5665,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131025478</v>
+        <v>131024506</v>
       </c>
       <c r="B47" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,42 +5676,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464380</v>
+        <v>464426</v>
       </c>
       <c r="R47" t="n">
-        <v>7042301</v>
+        <v>7042565</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5746,11 +5734,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5759,51 +5742,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025471</v>
+        <v>131025495</v>
       </c>
       <c r="B48" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5811,42 +5769,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464444</v>
+        <v>463986</v>
       </c>
       <c r="R48" t="n">
-        <v>7042363</v>
+        <v>7042522</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5883,7 +5829,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>I stående död klen gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5894,36 +5840,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5940,10 +5856,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025482</v>
+        <v>131025524</v>
       </c>
       <c r="B49" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5951,42 +5867,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464034</v>
+        <v>464041</v>
       </c>
       <c r="R49" t="n">
-        <v>7042322</v>
+        <v>7042631</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6023,7 +5931,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,31 +5942,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6075,10 +5958,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131024506</v>
+        <v>131025511</v>
       </c>
       <c r="B50" t="n">
-        <v>91836</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6086,30 +5969,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464426</v>
+        <v>464483</v>
       </c>
       <c r="R50" t="n">
-        <v>7042565</v>
+        <v>7042518</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6144,6 +6031,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6156,22 +6048,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025495</v>
+        <v>131025478</v>
       </c>
       <c r="B51" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6179,30 +6071,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>463986</v>
+        <v>464380</v>
       </c>
       <c r="R51" t="n">
-        <v>7042522</v>
+        <v>7042301</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6239,7 +6143,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6250,6 +6154,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6266,10 +6195,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025524</v>
+        <v>131025471</v>
       </c>
       <c r="B52" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,34 +6206,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464041</v>
+        <v>464444</v>
       </c>
       <c r="R52" t="n">
-        <v>7042631</v>
+        <v>7042363</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6341,7 +6278,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6352,6 +6289,36 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6368,10 +6335,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025511</v>
+        <v>131025482</v>
       </c>
       <c r="B53" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6379,34 +6346,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464483</v>
+        <v>464034</v>
       </c>
       <c r="R53" t="n">
-        <v>7042518</v>
+        <v>7042322</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6443,7 +6418,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6454,6 +6429,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6473,7 +6473,7 @@
         <v>131024511</v>
       </c>
       <c r="B54" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>131024510</v>
       </c>
       <c r="B55" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>131024507</v>
       </c>
       <c r="B56" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024463</v>
+        <v>131024501</v>
       </c>
       <c r="B57" t="n">
-        <v>57886</v>
+        <v>91813</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464371</v>
+        <v>464070</v>
       </c>
       <c r="R57" t="n">
-        <v>7042397</v>
+        <v>7042517</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6820,11 +6820,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6851,10 +6846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131025483</v>
+        <v>131025504</v>
       </c>
       <c r="B58" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6862,42 +6857,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464021</v>
+        <v>464204</v>
       </c>
       <c r="R58" t="n">
-        <v>7042325</v>
+        <v>7042559</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6934,7 +6921,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6945,31 +6932,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6986,10 +6948,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131025469</v>
+        <v>131024463</v>
       </c>
       <c r="B59" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7015,24 +6977,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464464</v>
+        <v>464371</v>
       </c>
       <c r="R59" t="n">
-        <v>7042544</v>
+        <v>7042397</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7069,7 +7023,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7080,51 +7034,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131024501</v>
+        <v>131025483</v>
       </c>
       <c r="B60" t="n">
-        <v>91812</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7132,34 +7061,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464070</v>
+        <v>464021</v>
       </c>
       <c r="R60" t="n">
-        <v>7042517</v>
+        <v>7042325</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7194,6 +7131,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7202,26 +7144,51 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131025504</v>
+        <v>131025469</v>
       </c>
       <c r="B61" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7229,34 +7196,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464204</v>
+        <v>464464</v>
       </c>
       <c r="R61" t="n">
-        <v>7042559</v>
+        <v>7042544</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7293,7 +7268,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7304,6 +7279,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7323,7 +7323,7 @@
         <v>131025508</v>
       </c>
       <c r="B62" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>131024460</v>
       </c>
       <c r="B63" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>131024450</v>
       </c>
       <c r="B64" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7626,27 +7626,27 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131024494</v>
+        <v>131024456</v>
       </c>
       <c r="B65" t="n">
-        <v>57990</v>
+        <v>57887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7654,29 +7654,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464304</v>
+        <v>464439</v>
       </c>
       <c r="R65" t="n">
-        <v>7042379</v>
+        <v>7042505</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7709,6 +7697,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7738,7 +7731,7 @@
         <v>131024509</v>
       </c>
       <c r="B66" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7828,27 +7821,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131024456</v>
+        <v>131024494</v>
       </c>
       <c r="B67" t="n">
-        <v>57886</v>
+        <v>57991</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7856,17 +7849,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464439</v>
+        <v>464304</v>
       </c>
       <c r="R67" t="n">
-        <v>7042505</v>
+        <v>7042379</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7899,11 +7904,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7933,7 +7933,7 @@
         <v>131025516</v>
       </c>
       <c r="B68" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>131025479</v>
       </c>
       <c r="B69" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>131024472</v>
       </c>
       <c r="B70" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8269,10 +8269,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131024477</v>
+        <v>131025481</v>
       </c>
       <c r="B71" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8298,16 +8298,24 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464028</v>
+        <v>464066</v>
       </c>
       <c r="R71" t="n">
-        <v>7042322</v>
+        <v>7042307</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8344,7 +8352,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8355,26 +8363,51 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131025481</v>
+        <v>131024477</v>
       </c>
       <c r="B72" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8400,24 +8433,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464066</v>
+        <v>464028</v>
       </c>
       <c r="R72" t="n">
-        <v>7042307</v>
+        <v>7042322</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8454,7 +8479,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8465,41 +8490,16 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8509,7 +8509,7 @@
         <v>131025521</v>
       </c>
       <c r="B73" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>131024453</v>
       </c>
       <c r="B74" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>131024451</v>
       </c>
       <c r="B75" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>131025480</v>
       </c>
       <c r="B76" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8947,10 +8947,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131025490</v>
+        <v>131025492</v>
       </c>
       <c r="B77" t="n">
-        <v>80354</v>
+        <v>91813</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,28 +8958,28 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8989,10 +8989,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>463994</v>
+        <v>464400</v>
       </c>
       <c r="R77" t="n">
-        <v>7042378</v>
+        <v>7042294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9049,22 +9049,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9082,10 +9082,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131025492</v>
+        <v>131025490</v>
       </c>
       <c r="B78" t="n">
-        <v>91812</v>
+        <v>80355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,28 +9093,28 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464400</v>
+        <v>463994</v>
       </c>
       <c r="R78" t="n">
-        <v>7042294</v>
+        <v>7042378</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9184,22 +9184,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9220,7 +9220,7 @@
         <v>131025523</v>
       </c>
       <c r="B79" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>131025503</v>
       </c>
       <c r="B80" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>131024470</v>
       </c>
       <c r="B81" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>131024461</v>
       </c>
       <c r="B82" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>131025520</v>
       </c>
       <c r="B83" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>131024505</v>
       </c>
       <c r="B84" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>131024508</v>
       </c>
       <c r="B85" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>131025475</v>
       </c>
       <c r="B86" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>131024473</v>
       </c>
       <c r="B87" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>131025477</v>
       </c>
       <c r="B88" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131025496</v>
+        <v>131024475</v>
       </c>
       <c r="B89" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10296,34 +10296,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464485</v>
+        <v>464272</v>
       </c>
       <c r="R89" t="n">
-        <v>7042454</v>
+        <v>7042273</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10375,22 +10375,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131025515</v>
+        <v>131025496</v>
       </c>
       <c r="B90" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464430</v>
+        <v>464485</v>
       </c>
       <c r="R90" t="n">
-        <v>7042344</v>
+        <v>7042454</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131024475</v>
+        <v>131025515</v>
       </c>
       <c r="B91" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10500,34 +10500,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464272</v>
+        <v>464430</v>
       </c>
       <c r="R91" t="n">
-        <v>7042273</v>
+        <v>7042344</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10579,12 +10579,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10594,7 +10594,7 @@
         <v>131024455</v>
       </c>
       <c r="B92" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>131024466</v>
       </c>
       <c r="B93" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>131024512</v>
       </c>
       <c r="B94" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>131025473</v>
       </c>
       <c r="B95" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>131024452</v>
       </c>
       <c r="B96" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>131025484</v>
       </c>
       <c r="B97" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>131025507</v>
       </c>
       <c r="B98" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131025505</v>
+        <v>131024500</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464214</v>
+        <v>463777</v>
       </c>
       <c r="R2" t="n">
-        <v>7042578</v>
+        <v>7042582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,11 +748,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131025514</v>
+        <v>131024501</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464434</v>
+        <v>464070</v>
       </c>
       <c r="R3" t="n">
-        <v>7042377</v>
+        <v>7042517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,11 +845,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar vid en lucka.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131024454</v>
+        <v>131025492</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,34 +880,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464321</v>
+        <v>464400</v>
       </c>
       <c r="R4" t="n">
-        <v>7042482</v>
+        <v>7042294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +951,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,28 +960,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131025513</v>
+        <v>131025489</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +1015,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464484</v>
+        <v>464035</v>
       </c>
       <c r="R5" t="n">
-        <v>7042425</v>
+        <v>7042354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1086,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Växer på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,8 +1095,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1083,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131025526</v>
+        <v>131025490</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1150,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464101</v>
+        <v>463994</v>
       </c>
       <c r="R6" t="n">
-        <v>7042665</v>
+        <v>7042378</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,8 +1230,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1185,45 +1274,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131024469</v>
+        <v>131025496</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464325</v>
+        <v>464485</v>
       </c>
       <c r="R7" t="n">
-        <v>7042323</v>
+        <v>7042454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1349,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,65 +1364,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131025467</v>
+        <v>131025502</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464403</v>
+        <v>464177</v>
       </c>
       <c r="R8" t="n">
-        <v>7042578</v>
+        <v>7042606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1451,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, tydliga på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,31 +1462,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1422,14 +1478,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131025506</v>
+        <v>131025503</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1457,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464253</v>
+        <v>464158</v>
       </c>
       <c r="R9" t="n">
-        <v>7042536</v>
+        <v>7042548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,7 +1553,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en tydligt gammal gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,14 +1580,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131025502</v>
+        <v>131025504</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1559,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464177</v>
+        <v>464204</v>
       </c>
       <c r="R10" t="n">
-        <v>7042606</v>
+        <v>7042559</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1626,14 +1682,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131025519</v>
+        <v>131025505</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1661,10 +1717,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464076</v>
+        <v>464214</v>
       </c>
       <c r="R11" t="n">
-        <v>7042281</v>
+        <v>7042578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,14 +1784,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131025512</v>
+        <v>131025506</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1763,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464451</v>
+        <v>464253</v>
       </c>
       <c r="R12" t="n">
-        <v>7042487</v>
+        <v>7042536</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,7 +1859,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>På en tydligt gammal gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,14 +1886,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131025518</v>
+        <v>131025507</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1865,10 +1921,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464161</v>
+        <v>464297</v>
       </c>
       <c r="R13" t="n">
-        <v>7042247</v>
+        <v>7042525</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1961,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Långväxta bålar på gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,53 +1988,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131025488</v>
+        <v>131025508</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463958</v>
+        <v>464310</v>
       </c>
       <c r="R14" t="n">
-        <v>7042484</v>
+        <v>7042565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,7 +2063,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen av en levande gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,31 +2074,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2067,30 +2090,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131025494</v>
+        <v>131025509</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2098,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464471</v>
+        <v>464380</v>
       </c>
       <c r="R15" t="n">
-        <v>7042462</v>
+        <v>7042615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2165,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I granstubbe.</t>
+          <t>På en gammal gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,45 +2192,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131024467</v>
+        <v>131025510</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464322</v>
+        <v>464463</v>
       </c>
       <c r="R16" t="n">
-        <v>7042355</v>
+        <v>7042542</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,7 +2267,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,65 +2282,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131025463</v>
+        <v>131025511</v>
       </c>
       <c r="B17" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464211</v>
+        <v>464483</v>
       </c>
       <c r="R17" t="n">
-        <v>7042581</v>
+        <v>7042518</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2369,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2361,31 +2380,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2402,45 +2396,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131024458</v>
+        <v>131025512</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464405</v>
+        <v>464451</v>
       </c>
       <c r="R18" t="n">
-        <v>7042391</v>
+        <v>7042487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,7 +2471,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,26 +2486,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131025525</v>
+        <v>131025513</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2539,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464067</v>
+        <v>464484</v>
       </c>
       <c r="R19" t="n">
-        <v>7042585</v>
+        <v>7042425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,14 +2600,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131025510</v>
+        <v>131025514</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2641,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464463</v>
+        <v>464434</v>
       </c>
       <c r="R20" t="n">
-        <v>7042542</v>
+        <v>7042377</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2675,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På flera granar vid en lucka.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,42 +2702,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131024468</v>
+        <v>131025515</v>
       </c>
       <c r="B21" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464332</v>
+        <v>464430</v>
       </c>
       <c r="R21" t="n">
         <v>7042344</v>
@@ -2783,7 +2777,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,57 +2792,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131024464</v>
+        <v>131025516</v>
       </c>
       <c r="B22" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464337</v>
+        <v>464319</v>
       </c>
       <c r="R22" t="n">
-        <v>7042380</v>
+        <v>7042262</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2885,7 +2879,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2900,65 +2894,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131025468</v>
+        <v>131025517</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464445</v>
+        <v>464199</v>
       </c>
       <c r="R23" t="n">
-        <v>7042578</v>
+        <v>7042210</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,31 +2992,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3047,14 +3008,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131025528</v>
+        <v>131025518</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3082,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464199</v>
+        <v>464161</v>
       </c>
       <c r="R24" t="n">
-        <v>7042793</v>
+        <v>7042247</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3122,7 +3083,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3149,45 +3110,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131024474</v>
+        <v>131025519</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464280</v>
+        <v>464076</v>
       </c>
       <c r="R25" t="n">
-        <v>7042322</v>
+        <v>7042281</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,7 +3185,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3239,57 +3200,57 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131024476</v>
+        <v>131025520</v>
       </c>
       <c r="B26" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464255</v>
+        <v>464027</v>
       </c>
       <c r="R26" t="n">
-        <v>7042273</v>
+        <v>7042318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3326,7 +3287,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,65 +3302,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131025474</v>
+        <v>131025521</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464391</v>
+        <v>464007</v>
       </c>
       <c r="R27" t="n">
-        <v>7042299</v>
+        <v>7042409</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,7 +3389,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,31 +3400,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3488,53 +3416,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131025470</v>
+        <v>131025522</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464484</v>
+        <v>463978</v>
       </c>
       <c r="R28" t="n">
-        <v>7042508</v>
+        <v>7042528</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3571,7 +3491,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På en stående död gran med full längd (36 cm bhd).</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3582,31 +3502,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3623,45 +3518,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131024449</v>
+        <v>131025523</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464183</v>
+        <v>463999</v>
       </c>
       <c r="R29" t="n">
-        <v>7042531</v>
+        <v>7042559</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3698,7 +3593,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,65 +3608,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131025485</v>
+        <v>131025524</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464186</v>
+        <v>464041</v>
       </c>
       <c r="R30" t="n">
-        <v>7042779</v>
+        <v>7042631</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,7 +3695,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3819,31 +3706,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3860,14 +3722,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131025509</v>
+        <v>131025525</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3895,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464380</v>
+        <v>464067</v>
       </c>
       <c r="R31" t="n">
-        <v>7042615</v>
+        <v>7042585</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3935,7 +3797,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På en gammal gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3962,14 +3824,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131025522</v>
+        <v>131025526</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3997,10 +3859,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>463978</v>
+        <v>464101</v>
       </c>
       <c r="R32" t="n">
-        <v>7042528</v>
+        <v>7042665</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4037,7 +3899,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På en stående död gran med full längd (36 cm bhd).</t>
+          <t>På gamgran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4064,45 +3926,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131024465</v>
+        <v>131025527</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464328</v>
+        <v>464174</v>
       </c>
       <c r="R33" t="n">
-        <v>7042367</v>
+        <v>7042780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4139,7 +4001,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4154,65 +4016,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131024446</v>
+        <v>131025528</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>463828</v>
+        <v>464199</v>
       </c>
       <c r="R34" t="n">
-        <v>7042514</v>
+        <v>7042793</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4249,14 +4103,14 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran</t>
+          <t>Gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4264,39 +4118,39 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131025464</v>
+        <v>131025488</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4309,7 +4163,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4319,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464210</v>
+        <v>463958</v>
       </c>
       <c r="R35" t="n">
-        <v>7042574</v>
+        <v>7042484</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4359,7 +4213,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Hackspår i stambasen av en levande gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4373,7 +4227,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4411,10 +4265,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131025527</v>
+        <v>131024446</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4422,34 +4276,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464174</v>
+        <v>463828</v>
       </c>
       <c r="R36" t="n">
-        <v>7042780</v>
+        <v>7042514</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4486,14 +4348,14 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Gammalt bohål i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -4501,22 +4363,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131025517</v>
+        <v>131024448</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4524,34 +4386,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464199</v>
+        <v>464165</v>
       </c>
       <c r="R37" t="n">
-        <v>7042210</v>
+        <v>7042546</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4588,7 +4450,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,22 +4465,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131025489</v>
+        <v>131024449</v>
       </c>
       <c r="B38" t="n">
-        <v>80355</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4626,41 +4488,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464035</v>
+        <v>464183</v>
       </c>
       <c r="R38" t="n">
-        <v>7042354</v>
+        <v>7042531</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4697,7 +4552,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Växer på en grov gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4706,54 +4561,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131025465</v>
+        <v>131024450</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,24 +4608,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464268</v>
+        <v>464273</v>
       </c>
       <c r="R39" t="n">
-        <v>7042527</v>
+        <v>7042500</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4833,7 +4654,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4844,51 +4665,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131024448</v>
+        <v>131024451</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,10 +4716,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464165</v>
+        <v>464275</v>
       </c>
       <c r="R40" t="n">
-        <v>7042546</v>
+        <v>7042455</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4960,7 +4756,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4987,10 +4783,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131024478</v>
+        <v>131024452</v>
       </c>
       <c r="B41" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5022,10 +4818,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464232</v>
+        <v>464339</v>
       </c>
       <c r="R41" t="n">
-        <v>7042762</v>
+        <v>7042474</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5089,10 +4885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131025472</v>
+        <v>131024453</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5118,24 +4914,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464419</v>
+        <v>464327</v>
       </c>
       <c r="R42" t="n">
-        <v>7042316</v>
+        <v>7042477</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5172,7 +4960,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5183,51 +4971,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131024462</v>
+        <v>131024454</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5259,10 +5022,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464376</v>
+        <v>464321</v>
       </c>
       <c r="R43" t="n">
-        <v>7042402</v>
+        <v>7042482</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5326,10 +5089,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131025466</v>
+        <v>131024455</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,24 +5118,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464389</v>
+        <v>464454</v>
       </c>
       <c r="R44" t="n">
-        <v>7042585</v>
+        <v>7042523</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5409,7 +5164,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5420,51 +5175,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131024459</v>
+        <v>131024456</v>
       </c>
       <c r="B45" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5496,10 +5226,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464397</v>
+        <v>464439</v>
       </c>
       <c r="R45" t="n">
-        <v>7042399</v>
+        <v>7042505</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5536,7 +5266,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5566,7 +5296,7 @@
         <v>131024457</v>
       </c>
       <c r="B46" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5665,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131024506</v>
+        <v>131024458</v>
       </c>
       <c r="B47" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5676,19 +5406,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5696,10 +5430,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464426</v>
+        <v>464405</v>
       </c>
       <c r="R47" t="n">
-        <v>7042565</v>
+        <v>7042391</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5732,6 +5466,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5758,10 +5497,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131025495</v>
+        <v>131024459</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5769,30 +5508,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>463986</v>
+        <v>464397</v>
       </c>
       <c r="R48" t="n">
-        <v>7042522</v>
+        <v>7042399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5829,7 +5572,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I stående död klen gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,22 +5587,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131025524</v>
+        <v>131024460</v>
       </c>
       <c r="B49" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5867,34 +5610,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464041</v>
+        <v>464385</v>
       </c>
       <c r="R49" t="n">
-        <v>7042631</v>
+        <v>7042401</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5931,7 +5674,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gamgran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5946,22 +5689,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131025511</v>
+        <v>131024461</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5969,34 +5712,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464483</v>
+        <v>464377</v>
       </c>
       <c r="R50" t="n">
-        <v>7042518</v>
+        <v>7042402</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6033,7 +5776,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6048,22 +5791,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131025478</v>
+        <v>131024462</v>
       </c>
       <c r="B51" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,24 +5832,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464380</v>
+        <v>464376</v>
       </c>
       <c r="R51" t="n">
-        <v>7042301</v>
+        <v>7042402</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6143,7 +5878,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6154,51 +5889,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131025471</v>
+        <v>131024463</v>
       </c>
       <c r="B52" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6224,24 +5934,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464444</v>
+        <v>464371</v>
       </c>
       <c r="R52" t="n">
-        <v>7042363</v>
+        <v>7042397</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6278,7 +5980,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6289,56 +5991,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131025482</v>
+        <v>131024464</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6364,24 +6036,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464034</v>
+        <v>464337</v>
       </c>
       <c r="R53" t="n">
-        <v>7042322</v>
+        <v>7042380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6418,7 +6082,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,51 +6093,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131024511</v>
+        <v>131024465</v>
       </c>
       <c r="B54" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6481,19 +6120,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6501,10 +6144,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>463866</v>
+        <v>464328</v>
       </c>
       <c r="R54" t="n">
-        <v>7042468</v>
+        <v>7042367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6537,6 +6180,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6563,10 +6211,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131024510</v>
+        <v>131024466</v>
       </c>
       <c r="B55" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6574,19 +6222,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6594,10 +6246,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464031</v>
+        <v>464319</v>
       </c>
       <c r="R55" t="n">
-        <v>7042403</v>
+        <v>7042385</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6630,6 +6282,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6656,10 +6313,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131024507</v>
+        <v>131024467</v>
       </c>
       <c r="B56" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6667,19 +6324,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6687,10 +6348,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464395</v>
+        <v>464322</v>
       </c>
       <c r="R56" t="n">
-        <v>7042406</v>
+        <v>7042355</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6723,6 +6384,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,10 +6415,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131024501</v>
+        <v>131024468</v>
       </c>
       <c r="B57" t="n">
-        <v>91813</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6760,21 +6426,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6784,10 +6450,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464070</v>
+        <v>464332</v>
       </c>
       <c r="R57" t="n">
-        <v>7042517</v>
+        <v>7042344</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6820,6 +6486,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6846,10 +6517,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131025504</v>
+        <v>131024469</v>
       </c>
       <c r="B58" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6857,34 +6528,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464204</v>
+        <v>464325</v>
       </c>
       <c r="R58" t="n">
-        <v>7042559</v>
+        <v>7042323</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6921,7 +6592,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6936,22 +6607,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131024463</v>
+        <v>131024470</v>
       </c>
       <c r="B59" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6983,10 +6654,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464371</v>
+        <v>464325</v>
       </c>
       <c r="R59" t="n">
-        <v>7042397</v>
+        <v>7042334</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7023,7 +6694,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7050,10 +6721,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131025483</v>
+        <v>131024472</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7079,24 +6750,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464021</v>
+        <v>464305</v>
       </c>
       <c r="R60" t="n">
-        <v>7042325</v>
+        <v>7042324</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7133,7 +6796,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7144,51 +6807,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131025469</v>
+        <v>131024473</v>
       </c>
       <c r="B61" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7214,24 +6852,16 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464464</v>
+        <v>464305</v>
       </c>
       <c r="R61" t="n">
-        <v>7042544</v>
+        <v>7042334</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7268,7 +6898,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en granhögstubbe.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7279,51 +6909,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131025508</v>
+        <v>131024474</v>
       </c>
       <c r="B62" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7331,34 +6936,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
+          <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464310</v>
+        <v>464280</v>
       </c>
       <c r="R62" t="n">
-        <v>7042565</v>
+        <v>7042322</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7395,7 +7000,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7410,22 +7015,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131024460</v>
+        <v>131024475</v>
       </c>
       <c r="B63" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7457,10 +7062,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464385</v>
+        <v>464272</v>
       </c>
       <c r="R63" t="n">
-        <v>7042401</v>
+        <v>7042273</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7524,10 +7129,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131024450</v>
+        <v>131024476</v>
       </c>
       <c r="B64" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7559,10 +7164,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464273</v>
+        <v>464255</v>
       </c>
       <c r="R64" t="n">
-        <v>7042500</v>
+        <v>7042273</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7626,10 +7231,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131024456</v>
+        <v>131024477</v>
       </c>
       <c r="B65" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7661,10 +7266,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464439</v>
+        <v>464028</v>
       </c>
       <c r="R65" t="n">
-        <v>7042505</v>
+        <v>7042322</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7701,7 +7306,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7728,10 +7333,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131024509</v>
+        <v>131024478</v>
       </c>
       <c r="B66" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7739,19 +7344,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7759,10 +7368,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464214</v>
+        <v>464232</v>
       </c>
       <c r="R66" t="n">
-        <v>7042282</v>
+        <v>7042762</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7795,6 +7404,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7821,27 +7435,27 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131024494</v>
+        <v>131025463</v>
       </c>
       <c r="B67" t="n">
-        <v>57991</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7849,29 +7463,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464304</v>
+        <v>464211</v>
       </c>
       <c r="R67" t="n">
-        <v>7042379</v>
+        <v>7042581</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7906,6 +7516,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7914,26 +7529,51 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131025516</v>
+        <v>131025464</v>
       </c>
       <c r="B68" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7941,34 +7581,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464319</v>
+        <v>464210</v>
       </c>
       <c r="R68" t="n">
-        <v>7042262</v>
+        <v>7042574</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8005,7 +7653,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8016,6 +7664,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8032,10 +7705,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131025479</v>
+        <v>131025465</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8065,7 +7738,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -8075,10 +7748,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464380</v>
+        <v>464268</v>
       </c>
       <c r="R69" t="n">
-        <v>7042291</v>
+        <v>7042527</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8115,7 +7788,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8129,7 +7802,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -8144,12 +7817,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8167,10 +7840,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131024472</v>
+        <v>131025466</v>
       </c>
       <c r="B70" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8196,16 +7869,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464305</v>
+        <v>464389</v>
       </c>
       <c r="R70" t="n">
-        <v>7042324</v>
+        <v>7042585</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8242,7 +7923,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en stående död gran med 20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8253,26 +7934,51 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131025481</v>
+        <v>131025467</v>
       </c>
       <c r="B71" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8302,7 +8008,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -8312,10 +8018,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464066</v>
+        <v>464403</v>
       </c>
       <c r="R71" t="n">
-        <v>7042307</v>
+        <v>7042578</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8352,7 +8058,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska och äldre, tydliga på en gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8404,10 +8110,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131024477</v>
+        <v>131025468</v>
       </c>
       <c r="B72" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8433,16 +8139,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464028</v>
+        <v>464445</v>
       </c>
       <c r="R72" t="n">
-        <v>7042322</v>
+        <v>7042578</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8479,7 +8193,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8490,26 +8204,51 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131025521</v>
+        <v>131025469</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8517,34 +8256,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464007</v>
+        <v>464464</v>
       </c>
       <c r="R73" t="n">
-        <v>7042409</v>
+        <v>7042544</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8581,7 +8328,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8592,6 +8339,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8608,10 +8380,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131024453</v>
+        <v>131025470</v>
       </c>
       <c r="B74" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8637,16 +8409,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464327</v>
+        <v>464484</v>
       </c>
       <c r="R74" t="n">
-        <v>7042477</v>
+        <v>7042508</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8683,7 +8463,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8694,26 +8474,51 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131024451</v>
+        <v>131025471</v>
       </c>
       <c r="B75" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8739,16 +8544,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464275</v>
+        <v>464444</v>
       </c>
       <c r="R75" t="n">
-        <v>7042455</v>
+        <v>7042363</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8785,7 +8598,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre, på stambasen av en böjd gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8796,26 +8609,56 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131025480</v>
+        <v>131025472</v>
       </c>
       <c r="B76" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8855,10 +8698,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464378</v>
+        <v>464419</v>
       </c>
       <c r="R76" t="n">
-        <v>7042302</v>
+        <v>7042316</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8895,7 +8738,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8924,12 +8767,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8947,10 +8790,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131025492</v>
+        <v>131025473</v>
       </c>
       <c r="B77" t="n">
-        <v>91813</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8958,28 +8801,29 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -8989,10 +8833,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464400</v>
+        <v>464413</v>
       </c>
       <c r="R77" t="n">
-        <v>7042294</v>
+        <v>7042312</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9029,7 +8873,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, färska och äldre, längs ett par meter på en gran med spår av rikligt kåda-flöde.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9038,13 +8882,17 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -9082,10 +8930,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131025490</v>
+        <v>131025474</v>
       </c>
       <c r="B78" t="n">
-        <v>80355</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9093,28 +8941,29 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
@@ -9124,10 +8973,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>463994</v>
+        <v>464391</v>
       </c>
       <c r="R78" t="n">
-        <v>7042378</v>
+        <v>7042299</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9164,7 +9013,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav på en grov gammal sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9173,7 +9022,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9184,22 +9032,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9217,10 +9065,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131025523</v>
+        <v>131025475</v>
       </c>
       <c r="B79" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9228,34 +9076,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>463999</v>
+        <v>464393</v>
       </c>
       <c r="R79" t="n">
-        <v>7042559</v>
+        <v>7042284</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9292,7 +9148,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar I gles  gammal granskog.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9303,6 +9159,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9319,10 +9200,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131025503</v>
+        <v>131025477</v>
       </c>
       <c r="B80" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9330,34 +9211,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464158</v>
+        <v>464374</v>
       </c>
       <c r="R80" t="n">
-        <v>7042548</v>
+        <v>7042300</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9394,7 +9283,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9405,6 +9294,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9421,10 +9335,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131024470</v>
+        <v>131025478</v>
       </c>
       <c r="B81" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9450,16 +9364,24 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464325</v>
+        <v>464380</v>
       </c>
       <c r="R81" t="n">
-        <v>7042334</v>
+        <v>7042301</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9496,7 +9418,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en levande gran. Medelhögt livsmiljövärde för tretåig hackspett på fyndplatsen baserat på volym stående död ved.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9507,26 +9429,51 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131024461</v>
+        <v>131025479</v>
       </c>
       <c r="B82" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9552,16 +9499,24 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464377</v>
+        <v>464380</v>
       </c>
       <c r="R82" t="n">
-        <v>7042402</v>
+        <v>7042291</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9598,7 +9553,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD 20 cm).</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9609,26 +9564,51 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131025520</v>
+        <v>131025480</v>
       </c>
       <c r="B83" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9636,34 +9616,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464027</v>
+        <v>464378</v>
       </c>
       <c r="R83" t="n">
-        <v>7042318</v>
+        <v>7042302</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9700,7 +9688,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack, äldre, på stambasen av en stående död gran (BHD &gt;10cm).</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9711,6 +9699,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9727,10 +9740,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131024505</v>
+        <v>131025481</v>
       </c>
       <c r="B84" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9738,30 +9751,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464276</v>
+        <v>464066</v>
       </c>
       <c r="R84" t="n">
-        <v>7042457</v>
+        <v>7042307</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9796,6 +9821,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9804,26 +9834,51 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131024508</v>
+        <v>131025482</v>
       </c>
       <c r="B85" t="n">
-        <v>91837</v>
+        <v>57953</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9831,30 +9886,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464083</v>
+        <v>464034</v>
       </c>
       <c r="R85" t="n">
-        <v>7042298</v>
+        <v>7042322</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9889,6 +9956,11 @@
           <t>2026-02-03</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9897,26 +9969,51 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131025475</v>
+        <v>131025483</v>
       </c>
       <c r="B86" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9946,7 +10043,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9956,10 +10053,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464393</v>
+        <v>464021</v>
       </c>
       <c r="R86" t="n">
-        <v>7042284</v>
+        <v>7042325</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9996,7 +10093,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, längs minst 6 meter på en gran ca 4 meter från strandkanten. Rikligt med spår av rinnande kåda/sav på granens stam.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10048,10 +10145,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131024473</v>
+        <v>131025484</v>
       </c>
       <c r="B87" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10077,16 +10174,24 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sjöarsjön N, Jmt</t>
+          <t>Sjöarsjön Nordöst, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464305</v>
+        <v>464099</v>
       </c>
       <c r="R87" t="n">
-        <v>7042334</v>
+        <v>7042646</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10123,7 +10228,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre, tydliga på gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10134,26 +10239,51 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131025477</v>
+        <v>131025485</v>
       </c>
       <c r="B88" t="n">
-        <v>57887</v>
+        <v>57953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10193,10 +10323,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464374</v>
+        <v>464186</v>
       </c>
       <c r="R88" t="n">
-        <v>7042300</v>
+        <v>7042779</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10233,7 +10363,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10285,10 +10415,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131024475</v>
+        <v>131024494</v>
       </c>
       <c r="B89" t="n">
-        <v>57887</v>
+        <v>58057</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10296,16 +10426,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10313,17 +10443,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Sjöarsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464272</v>
+        <v>464304</v>
       </c>
       <c r="R89" t="n">
-        <v>7042273</v>
+        <v>7042379</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10358,11 +10500,6 @@
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10384,986 +10521,6 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>131025496</v>
-      </c>
-      <c r="B90" t="n">
-        <v>79249</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>464485</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7042454</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>131025515</v>
-      </c>
-      <c r="B91" t="n">
-        <v>79249</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>464430</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7042344</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>131024455</v>
-      </c>
-      <c r="B92" t="n">
-        <v>57887</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Sjöarsjön N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>464454</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7042523</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>131024466</v>
-      </c>
-      <c r="B93" t="n">
-        <v>57887</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Sjöarsjön N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>464319</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7042385</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>131024512</v>
-      </c>
-      <c r="B94" t="n">
-        <v>91837</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Sjöarsjön N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>464059</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7042514</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>131025473</v>
-      </c>
-      <c r="B95" t="n">
-        <v>57887</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>464413</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7042312</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack, färska och äldre, längs ett par meter på en gran med spår av rikligt kåda-flöde.</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>131024452</v>
-      </c>
-      <c r="B96" t="n">
-        <v>57887</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Sjöarsjön N, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>464339</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7042474</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>131025484</v>
-      </c>
-      <c r="B97" t="n">
-        <v>57887</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q97" t="n">
-        <v>464099</v>
-      </c>
-      <c r="R97" t="n">
-        <v>7042646</v>
-      </c>
-      <c r="S97" t="n">
-        <v>10</v>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, tydliga på gran.</t>
-        </is>
-      </c>
-      <c r="AD97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT97" t="inlineStr"/>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>131025507</v>
-      </c>
-      <c r="B98" t="n">
-        <v>79249</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Sjöarsjön Nordöst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q98" t="n">
-        <v>464297</v>
-      </c>
-      <c r="R98" t="n">
-        <v>7042525</v>
-      </c>
-      <c r="S98" t="n">
-        <v>10</v>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran i barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AD98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT98" t="inlineStr"/>
-      <c r="AW98" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62205-2025 artfynd.xlsx
+++ b/artfynd/A 62205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024501</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025492</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025489</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025490</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025496</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1679,6 +1724,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025504</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,6 +1831,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025505</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025506</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1985,6 +2045,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025507</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025508</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025509</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025510</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025511</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2495,6 +2580,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025512</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025513</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025514</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2801,6 +2901,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025515</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2903,6 +3008,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025516</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3005,6 +3115,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025517</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3107,6 +3222,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025518</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3209,6 +3329,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025519</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3311,6 +3436,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025520</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3413,6 +3543,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025521</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3515,6 +3650,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025522</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3617,6 +3757,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025523</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3719,6 +3864,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025524</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3821,6 +3971,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025525</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3923,6 +4078,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025526</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4025,6 +4185,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025527</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4127,6 +4292,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025528</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4262,6 +4432,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025488</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4372,6 +4547,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024446</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4474,6 +4654,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024448</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4576,6 +4761,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024449</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4678,6 +4868,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024450</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4780,6 +4975,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024451</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4882,6 +5082,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024452</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4984,6 +5189,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024453</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5086,6 +5296,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024454</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5188,6 +5403,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024455</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5290,6 +5510,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024456</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5392,6 +5617,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024457</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5494,6 +5724,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024458</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5596,6 +5831,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024459</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5698,6 +5938,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024460</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5800,6 +6045,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024461</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5902,6 +6152,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024462</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6004,6 +6259,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024463</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6106,6 +6366,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024464</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6208,6 +6473,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024465</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6310,6 +6580,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024466</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6412,6 +6687,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024467</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6514,6 +6794,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024468</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6616,6 +6901,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024469</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6718,6 +7008,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024470</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6820,6 +7115,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024472</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6922,6 +7222,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024473</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7024,6 +7329,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024474</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7126,6 +7436,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024475</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7228,6 +7543,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024476</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7330,6 +7650,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024477</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7432,6 +7757,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024478</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7567,6 +7897,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025463</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7702,6 +8037,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025464</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7837,6 +8177,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025465</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7972,6 +8317,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025466</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8107,6 +8457,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025467</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8242,6 +8597,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025468</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8377,6 +8737,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025469</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8512,6 +8877,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025470</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8652,6 +9022,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025471</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8787,6 +9162,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025472</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8927,6 +9307,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025473</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9062,6 +9447,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025474</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9197,6 +9587,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025475</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9332,6 +9727,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025477</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9467,6 +9867,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025478</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9602,6 +10007,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025479</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9737,6 +10147,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025480</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9872,6 +10287,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025481</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10007,6 +10427,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025482</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10142,6 +10567,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025483</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10277,6 +10707,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025484</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10412,6 +10847,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131025485</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10521,8 +10961,103 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131024494</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>